--- a/Job_Tracker_Mumbai_Java.xlsx
+++ b/Job_Tracker_Mumbai_Java.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Excluded" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$O$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$O$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -157,7 +157,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -236,6 +236,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -574,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:O98"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="13" min="1" max="1"/>
@@ -671,10 +683,10 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="14">
-      <c r="A2" s="16" t="n">
+      <c r="A2" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="27">
         <f>IF(OR(ISNUMBER(SEARCH("mumbai",E2)),ISNUMBER(SEARCH("thane",E2)),ISNUMBER(SEARCH("remote",E2))),"1 Mumbai/Remote",IF(OR(E2="",E2="Verify"),"2 Verify location","3 Other city"))</f>
         <v/>
       </c>
@@ -693,35 +705,35 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="27" t="inlineStr">
         <is>
           <t>5-8 yrs</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="G2" s="27" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="H2" s="18" t="n">
+      <c r="H2" s="28" t="n">
         <v>46305</v>
       </c>
-      <c r="I2" s="19">
+      <c r="I2" s="29">
         <f>IF(H2="","",TODAY()-H2)</f>
         <v/>
       </c>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="J2" s="27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K2" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L2" s="18" t="n"/>
-      <c r="M2" s="20" t="inlineStr">
+      <c r="K2" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L2" s="28" t="n"/>
+      <c r="M2" s="30" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -731,15 +743,15 @@
           <t>Listed Rs 14-24 LPA (Weekday)</t>
         </is>
       </c>
-      <c r="O2" s="18" t="n">
+      <c r="O2" s="28" t="n">
         <v>46309</v>
       </c>
     </row>
     <row r="3" ht="23.85" customHeight="1" s="14">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="27">
         <f>IF(OR(ISNUMBER(SEARCH("mumbai",E3)),ISNUMBER(SEARCH("thane",E3)),ISNUMBER(SEARCH("remote",E3))),"1 Mumbai/Remote",IF(OR(E3="",E3="Verify"),"2 Verify location","3 Other city"))</f>
         <v/>
       </c>
@@ -758,35 +770,35 @@
           <t>Remote</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="27" t="inlineStr">
         <is>
           <t>4-8 yrs</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="G3" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H3" s="18" t="n">
+      <c r="H3" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="29">
         <f>IF(H3="","",TODAY()-H3)</f>
         <v/>
       </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="J3" s="27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K3" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L3" s="18" t="n"/>
-      <c r="M3" s="20" t="inlineStr">
+      <c r="K3" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L3" s="28" t="n"/>
+      <c r="M3" s="30" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -796,15 +808,15 @@
           <t>Java 11/17+, Spring Boot, Spring Cloud. Recruiter-posted</t>
         </is>
       </c>
-      <c r="O3" s="18" t="n">
+      <c r="O3" s="28" t="n">
         <v>46309</v>
       </c>
     </row>
     <row r="4" ht="23.85" customHeight="1" s="14">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="27">
         <f>IF(OR(ISNUMBER(SEARCH("mumbai",E4)),ISNUMBER(SEARCH("thane",E4)),ISNUMBER(SEARCH("remote",E4))),"1 Mumbai/Remote",IF(OR(E4="",E4="Verify"),"2 Verify location","3 Other city"))</f>
         <v/>
       </c>
@@ -823,35 +835,35 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="H4" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I4" s="19">
+      <c r="I4" s="29">
         <f>IF(H4="","",TODAY()-H4)</f>
         <v/>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K4" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L4" s="18" t="n"/>
-      <c r="M4" s="20" t="inlineStr">
+      <c r="K4" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L4" s="28" t="n"/>
+      <c r="M4" s="30" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -861,15 +873,15 @@
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O4" s="18" t="n">
+      <c r="O4" s="28" t="n">
         <v>46309</v>
       </c>
     </row>
     <row r="5" ht="23.85" customHeight="1" s="14">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="27">
         <f>IF(OR(ISNUMBER(SEARCH("mumbai",E5)),ISNUMBER(SEARCH("thane",E5)),ISNUMBER(SEARCH("remote",E5))),"1 Mumbai/Remote",IF(OR(E5="",E5="Verify"),"2 Verify location","3 Other city"))</f>
         <v/>
       </c>
@@ -888,35 +900,35 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="29">
         <f>IF(H5="","",TODAY()-H5)</f>
         <v/>
       </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="J5" s="27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K5" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L5" s="18" t="n"/>
-      <c r="M5" s="20" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L5" s="28" t="n"/>
+      <c r="M5" s="30" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -926,15 +938,15 @@
           <t>Best fit: Kafka + your AI-assisted upgrade tool</t>
         </is>
       </c>
-      <c r="O5" s="18" t="n">
+      <c r="O5" s="28" t="n">
         <v>46309</v>
       </c>
     </row>
     <row r="6" ht="23.85" customHeight="1" s="14">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="27">
         <f>IF(OR(ISNUMBER(SEARCH("mumbai",E6)),ISNUMBER(SEARCH("thane",E6)),ISNUMBER(SEARCH("remote",E6))),"1 Mumbai/Remote",IF(OR(E6="",E6="Verify"),"2 Verify location","3 Other city"))</f>
         <v/>
       </c>
@@ -953,35 +965,35 @@
           <t>Mumbai / Thane / Navi Mumbai</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="27" t="inlineStr">
         <is>
           <t>4-8 yrs</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>Naukri</t>
         </is>
       </c>
-      <c r="H6" s="18" t="n">
+      <c r="H6" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="29">
         <f>IF(H6="","",TODAY()-H6)</f>
         <v/>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J6" s="27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L6" s="18" t="n"/>
-      <c r="M6" s="20" t="inlineStr">
+      <c r="K6" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L6" s="28" t="n"/>
+      <c r="M6" s="30" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -991,15 +1003,15 @@
           <t>Core Java, Kafka, SQL, Spring Boot, Microservices</t>
         </is>
       </c>
-      <c r="O6" s="18" t="n">
+      <c r="O6" s="28" t="n">
         <v>46309</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="14">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="27">
         <f>IF(OR(ISNUMBER(SEARCH("mumbai",E7)),ISNUMBER(SEARCH("thane",E7)),ISNUMBER(SEARCH("remote",E7))),"1 Mumbai/Remote",IF(OR(E7="",E7="Verify"),"2 Verify location","3 Other city"))</f>
         <v/>
       </c>
@@ -1018,35 +1030,35 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H7" s="18" t="n">
+      <c r="H7" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="29">
         <f>IF(H7="","",TODAY()-H7)</f>
         <v/>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J7" s="27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L7" s="18" t="n"/>
-      <c r="M7" s="20" t="inlineStr">
+      <c r="K7" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L7" s="28" t="n"/>
+      <c r="M7" s="30" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -1056,5277 +1068,5927 @@
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O7" s="18" t="n">
+      <c r="O7" s="28" t="n">
         <v>46309</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="14">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="27">
         <f>IF(OR(ISNUMBER(SEARCH("mumbai",E8)),ISNUMBER(SEARCH("thane",E8)),ISNUMBER(SEARCH("remote",E8))),"1 Mumbai/Remote",IF(OR(E8="",E8="Verify"),"2 Verify location","3 Other city"))</f>
         <v/>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
+          <t>Zenshastra</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Java Developer</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="G8" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I8" s="29">
+        <f>IF(H8="","",TODAY()-H8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K8" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L8" s="28" t="n"/>
+      <c r="M8" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N8" s="17" t="inlineStr">
+        <is>
+          <t>Auto-added; check company/location</t>
+        </is>
+      </c>
+      <c r="O8" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="14">
+      <c r="A9" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E9)),ISNUMBER(SEARCH("thane",E9)),ISNUMBER(SEARCH("remote",E9))),"1 Mumbai/Remote",IF(OR(E9="",E9="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>IMC Trading</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Software Engineer (Java) - Research Data Platform</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="G9" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I9" s="29">
+        <f>IF(H9="","",TODAY()-H9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K9" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L9" s="28" t="n"/>
+      <c r="M9" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t>Auto-added; check company/location</t>
+        </is>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="14">
+      <c r="A10" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E10)),ISNUMBER(SEARCH("thane",E10)),ISNUMBER(SEARCH("remote",E10))),"1 Mumbai/Remote",IF(OR(E10="",E10="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Data Eminence</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="G10" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H10" s="28" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I10" s="29">
+        <f>IF(H10="","",TODAY()-H10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K10" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L10" s="28" t="n"/>
+      <c r="M10" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N10" s="17" t="inlineStr">
+        <is>
+          <t>Auto-added; check company/location</t>
+        </is>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="14">
+      <c r="A11" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E11)),ISNUMBER(SEARCH("thane",E11)),ISNUMBER(SEARCH("remote",E11))),"1 Mumbai/Remote",IF(OR(E11="",E11="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
           <t>HYrEzy Tech Solutions</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Java Microservices Engineers - Remote</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F11" s="27" t="inlineStr">
         <is>
           <t>4-8 yrs</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H8" s="18" t="n">
+      <c r="H11" s="28" t="n">
         <v>46308</v>
       </c>
-      <c r="I8" s="19">
-        <f>IF(H8="","",TODAY()-H8)</f>
-        <v/>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L8" s="18" t="n"/>
-      <c r="M8" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="I11" s="29">
+        <f>IF(H11="","",TODAY()-H11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K11" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L11" s="28" t="n"/>
+      <c r="M11" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N11" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O8" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="14">
-      <c r="A9" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E9)),ISNUMBER(SEARCH("thane",E9)),ISNUMBER(SEARCH("remote",E9))),"1 Mumbai/Remote",IF(OR(E9="",E9="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="O11" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="12" ht="23.85" customHeight="1" s="14">
+      <c r="A12" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E12)),ISNUMBER(SEARCH("thane",E12)),ISNUMBER(SEARCH("remote",E12))),"1 Mumbai/Remote",IF(OR(E12="",E12="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>Capgemini</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Java with Kafka and AWS</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>Mumbai / Navi Mumbai / Bengaluru</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F12" s="27" t="inlineStr">
         <is>
           <t>6-11 yrs</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>Naukri</t>
         </is>
       </c>
-      <c r="H9" s="18" t="n">
+      <c r="H12" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="I9" s="19">
-        <f>IF(H9="","",TODAY()-H9)</f>
-        <v/>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L9" s="18" t="n"/>
-      <c r="M9" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="I12" s="29">
+        <f>IF(H12="","",TODAY()-H12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K12" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L12" s="28" t="n"/>
+      <c r="M12" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N12" s="17" t="inlineStr">
         <is>
           <t>Stretch on experience; stack matches. Hybrid</t>
         </is>
       </c>
-      <c r="O9" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="14">
-      <c r="A10" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E10)),ISNUMBER(SEARCH("thane",E10)),ISNUMBER(SEARCH("remote",E10))),"1 Mumbai/Remote",IF(OR(E10="",E10="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="O12" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="14">
+      <c r="A13" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E13)),ISNUMBER(SEARCH("thane",E13)),ISNUMBER(SEARCH("remote",E13))),"1 Mumbai/Remote",IF(OR(E13="",E13="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>Accenture</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>Full Stack Engineer (Java)</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F13" s="27" t="inlineStr">
         <is>
           <t>5+ yrs</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G13" s="27" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="H10" s="18" t="n">
+      <c r="H13" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="I10" s="19">
-        <f>IF(H10="","",TODAY()-H10)</f>
-        <v/>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L10" s="18" t="n"/>
-      <c r="M10" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="I13" s="29">
+        <f>IF(H13="","",TODAY()-H13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K13" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L13" s="28" t="n"/>
+      <c r="M13" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N13" s="17" t="inlineStr">
         <is>
           <t>Java full stack; Mumbai office</t>
         </is>
       </c>
-      <c r="O10" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="14">
-      <c r="A11" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E11)),ISNUMBER(SEARCH("thane",E11)),ISNUMBER(SEARCH("remote",E11))),"1 Mumbai/Remote",IF(OR(E11="",E11="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="O13" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="14">
+      <c r="A14" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E14)),ISNUMBER(SEARCH("thane",E14)),ISNUMBER(SEARCH("remote",E14))),"1 Mumbai/Remote",IF(OR(E14="",E14="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Mattecurve Technologies</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>Senior Java Software Engineer - Remote Contract</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F14" s="27" t="inlineStr">
         <is>
           <t>4+ yrs</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H11" s="18" t="n">
+      <c r="H14" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="I11" s="19">
-        <f>IF(H11="","",TODAY()-H11)</f>
-        <v/>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L11" s="18" t="n"/>
-      <c r="M11" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="I14" s="29">
+        <f>IF(H14="","",TODAY()-H14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K14" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L14" s="28" t="n"/>
+      <c r="M14" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N14" s="17" t="inlineStr">
         <is>
           <t>Contract role, not full-time</t>
         </is>
       </c>
-      <c r="O11" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="12" ht="23.85" customHeight="1" s="14">
-      <c r="A12" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E12)),ISNUMBER(SEARCH("thane",E12)),ISNUMBER(SEARCH("remote",E12))),"1 Mumbai/Remote",IF(OR(E12="",E12="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="O14" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="14">
+      <c r="A15" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E15)),ISNUMBER(SEARCH("thane",E15)),ISNUMBER(SEARCH("remote",E15))),"1 Mumbai/Remote",IF(OR(E15="",E15="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Delphie Consulting services</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>Senior Java Software Engineer</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F15" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G15" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="H15" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="I12" s="19">
-        <f>IF(H12="","",TODAY()-H12)</f>
-        <v/>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L12" s="18" t="n"/>
-      <c r="M12" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="I15" s="29">
+        <f>IF(H15="","",TODAY()-H15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K15" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L15" s="28" t="n"/>
+      <c r="M15" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N15" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O12" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="14">
-      <c r="A13" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E13)),ISNUMBER(SEARCH("thane",E13)),ISNUMBER(SEARCH("remote",E13))),"1 Mumbai/Remote",IF(OR(E13="",E13="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="O15" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="14">
+      <c r="A16" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E16)),ISNUMBER(SEARCH("thane",E16)),ISNUMBER(SEARCH("remote",E16))),"1 Mumbai/Remote",IF(OR(E16="",E16="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>Software Engineer III - Full Stack Developer - React, TypeScript + ...</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F16" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G16" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H13" s="18" t="n">
+      <c r="H16" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="I13" s="19">
-        <f>IF(H13="","",TODAY()-H13)</f>
-        <v/>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L13" s="18" t="n"/>
-      <c r="M13" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="I16" s="29">
+        <f>IF(H16="","",TODAY()-H16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K16" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L16" s="28" t="n"/>
+      <c r="M16" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N16" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O13" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="14">
-      <c r="A14" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E14)),ISNUMBER(SEARCH("thane",E14)),ISNUMBER(SEARCH("remote",E14))),"1 Mumbai/Remote",IF(OR(E14="",E14="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="O16" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="14">
+      <c r="A17" s="27" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E17)),ISNUMBER(SEARCH("thane",E17)),ISNUMBER(SEARCH("remote",E17))),"1 Mumbai/Remote",IF(OR(E17="",E17="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Senior Java Software Engineer — Remote Contract</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F17" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G17" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H14" s="18" t="n">
+      <c r="H17" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="I14" s="19">
-        <f>IF(H14="","",TODAY()-H14)</f>
-        <v/>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L14" s="18" t="n"/>
-      <c r="M14" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="I17" s="29">
+        <f>IF(H17="","",TODAY()-H17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K17" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L17" s="28" t="n"/>
+      <c r="M17" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N17" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O14" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="14">
-      <c r="A15" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E15)),ISNUMBER(SEARCH("thane",E15)),ISNUMBER(SEARCH("remote",E15))),"1 Mumbai/Remote",IF(OR(E15="",E15="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="O17" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="14">
+      <c r="A18" s="27" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E18)),ISNUMBER(SEARCH("thane",E18)),ISNUMBER(SEARCH("remote",E18))),"1 Mumbai/Remote",IF(OR(E18="",E18="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Naukri (company not shown)</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Java Spring Boot Developer</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F18" s="27" t="inlineStr">
         <is>
           <t>3-6 yrs</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G18" s="27" t="inlineStr">
         <is>
           <t>Naukri</t>
         </is>
       </c>
-      <c r="H15" s="18" t="n">
+      <c r="H18" s="28" t="n">
         <v>46306</v>
       </c>
-      <c r="I15" s="19">
-        <f>IF(H15="","",TODAY()-H15)</f>
-        <v/>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L15" s="18" t="n"/>
-      <c r="M15" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="I18" s="29">
+        <f>IF(H18="","",TODAY()-H18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K18" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L18" s="28" t="n"/>
+      <c r="M18" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N18" s="17" t="inlineStr">
         <is>
           <t>Hibernate, MySQL, Microservices</t>
         </is>
       </c>
-      <c r="O15" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="14">
-      <c r="A16" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E16)),ISNUMBER(SEARCH("thane",E16)),ISNUMBER(SEARCH("remote",E16))),"1 Mumbai/Remote",IF(OR(E16="",E16="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="O18" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="19" ht="23.85" customHeight="1" s="14">
+      <c r="A19" s="27" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E19)),ISNUMBER(SEARCH("thane",E19)),ISNUMBER(SEARCH("remote",E19))),"1 Mumbai/Remote",IF(OR(E19="",E19="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Mount Talent Consulting</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>Senior Java Developer - Backend Engineering</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F19" s="27" t="inlineStr">
         <is>
           <t>5+ yrs</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G19" s="27" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="H16" s="18" t="n">
+      <c r="H19" s="28" t="n">
         <v>46306</v>
       </c>
-      <c r="I16" s="19">
-        <f>IF(H16="","",TODAY()-H16)</f>
-        <v/>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L16" s="18" t="n"/>
-      <c r="M16" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="I19" s="29">
+        <f>IF(H19="","",TODAY()-H19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K19" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L19" s="28" t="n"/>
+      <c r="M19" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N19" s="17" t="inlineStr">
         <is>
           <t>Staffing agency</t>
         </is>
       </c>
-      <c r="O16" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="14">
-      <c r="A17" s="16" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E17)),ISNUMBER(SEARCH("thane",E17)),ISNUMBER(SEARCH("remote",E17))),"1 Mumbai/Remote",IF(OR(E17="",E17="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="O19" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="14">
+      <c r="A20" s="27" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E20)),ISNUMBER(SEARCH("thane",E20)),ISNUMBER(SEARCH("remote",E20))),"1 Mumbai/Remote",IF(OR(E20="",E20="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>Senior Java Full Stack Developer | Remote | Jobs In India</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F20" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G20" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H17" s="18" t="n">
+      <c r="H20" s="28" t="n">
         <v>46306</v>
       </c>
-      <c r="I17" s="19">
-        <f>IF(H17="","",TODAY()-H17)</f>
-        <v/>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L17" s="18" t="n"/>
-      <c r="M17" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="I20" s="29">
+        <f>IF(H20="","",TODAY()-H20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K20" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L20" s="28" t="n"/>
+      <c r="M20" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N20" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O17" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="14">
-      <c r="A18" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E18)),ISNUMBER(SEARCH("thane",E18)),ISNUMBER(SEARCH("remote",E18))),"1 Mumbai/Remote",IF(OR(E18="",E18="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="O20" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="14">
+      <c r="A21" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E21)),ISNUMBER(SEARCH("thane",E21)),ISNUMBER(SEARCH("remote",E21))),"1 Mumbai/Remote",IF(OR(E21="",E21="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>ICE</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>SDE II</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F21" s="27" t="inlineStr">
         <is>
           <t>2-3 yrs</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G21" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H18" s="18" t="n">
+      <c r="H21" s="28" t="n">
         <v>46306</v>
       </c>
-      <c r="I18" s="19">
-        <f>IF(H18="","",TODAY()-H18)</f>
-        <v/>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K18" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L18" s="18" t="n"/>
-      <c r="M18" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N18" s="17" t="inlineStr">
+      <c r="I21" s="29">
+        <f>IF(H21="","",TODAY()-H21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K21" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L21" s="28" t="n"/>
+      <c r="M21" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N21" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O18" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="19" ht="23.85" customHeight="1" s="14">
-      <c r="A19" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E19)),ISNUMBER(SEARCH("thane",E19)),ISNUMBER(SEARCH("remote",E19))),"1 Mumbai/Remote",IF(OR(E19="",E19="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="O21" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="14">
+      <c r="A22" s="27" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E22)),ISNUMBER(SEARCH("thane",E22)),ISNUMBER(SEARCH("remote",E22))),"1 Mumbai/Remote",IF(OR(E22="",E22="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>ICE</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>Full Stack Engineer - SDE II</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F22" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G22" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H19" s="18" t="n">
+      <c r="H22" s="28" t="n">
         <v>46306</v>
       </c>
-      <c r="I19" s="19">
-        <f>IF(H19="","",TODAY()-H19)</f>
-        <v/>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L19" s="18" t="n"/>
-      <c r="M19" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N19" s="17" t="inlineStr">
+      <c r="I22" s="29">
+        <f>IF(H22="","",TODAY()-H22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K22" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L22" s="28" t="n"/>
+      <c r="M22" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N22" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O19" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="14">
-      <c r="A20" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E20)),ISNUMBER(SEARCH("thane",E20)),ISNUMBER(SEARCH("remote",E20))),"1 Mumbai/Remote",IF(OR(E20="",E20="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="O22" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="14">
+      <c r="A23" s="27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E23)),ISNUMBER(SEARCH("thane",E23)),ISNUMBER(SEARCH("remote",E23))),"1 Mumbai/Remote",IF(OR(E23="",E23="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>Nium</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>SDE II - Full Stack Engineer</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F23" s="27" t="inlineStr">
         <is>
           <t>2-3 yrs</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G23" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H20" s="18" t="n">
+      <c r="H23" s="28" t="n">
         <v>46306</v>
       </c>
-      <c r="I20" s="19">
-        <f>IF(H20="","",TODAY()-H20)</f>
-        <v/>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L20" s="18" t="n"/>
-      <c r="M20" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N20" s="17" t="inlineStr">
+      <c r="I23" s="29">
+        <f>IF(H23="","",TODAY()-H23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K23" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L23" s="28" t="n"/>
+      <c r="M23" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N23" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O20" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="14">
-      <c r="A21" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E21)),ISNUMBER(SEARCH("thane",E21)),ISNUMBER(SEARCH("remote",E21))),"1 Mumbai/Remote",IF(OR(E21="",E21="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="O23" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="24" ht="23.85" customHeight="1" s="14">
+      <c r="A24" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E24)),ISNUMBER(SEARCH("thane",E24)),ISNUMBER(SEARCH("remote",E24))),"1 Mumbai/Remote",IF(OR(E24="",E24="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>Experis</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>Backend Developer / Software Engineer</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>Thane / Mumbai</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F24" s="27" t="inlineStr">
         <is>
           <t>5+ yrs</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G24" s="27" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="H21" s="18" t="n">
+      <c r="H24" s="28" t="n">
         <v>46305</v>
       </c>
-      <c r="I21" s="19">
-        <f>IF(H21="","",TODAY()-H21)</f>
-        <v/>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K21" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L21" s="18" t="n"/>
-      <c r="M21" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N21" s="17" t="inlineStr">
+      <c r="I24" s="29">
+        <f>IF(H24="","",TODAY()-H24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K24" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L24" s="28" t="n"/>
+      <c r="M24" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N24" s="17" t="inlineStr">
         <is>
           <t>Staffing agency</t>
         </is>
       </c>
-      <c r="O21" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="14">
-      <c r="A22" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E22)),ISNUMBER(SEARCH("thane",E22)),ISNUMBER(SEARCH("remote",E22))),"1 Mumbai/Remote",IF(OR(E22="",E22="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="O24" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="14">
+      <c r="A25" s="27" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E25)),ISNUMBER(SEARCH("thane",E25)),ISNUMBER(SEARCH("remote",E25))),"1 Mumbai/Remote",IF(OR(E25="",E25="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>Algodomain</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>Senior Java Backend Engineer</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F25" s="27" t="inlineStr">
         <is>
           <t>5+ yrs</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G25" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H22" s="18" t="n">
+      <c r="H25" s="28" t="n">
         <v>46305</v>
       </c>
-      <c r="I22" s="19">
-        <f>IF(H22="","",TODAY()-H22)</f>
-        <v/>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K22" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L22" s="18" t="n"/>
-      <c r="M22" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N22" s="17" t="inlineStr">
+      <c r="I25" s="29">
+        <f>IF(H25="","",TODAY()-H25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K25" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L25" s="28" t="n"/>
+      <c r="M25" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N25" s="17" t="inlineStr">
         <is>
           <t>Java 17, Spring Boot 3, Kubernetes. Listed Chicago/London/Remote - confirm India is allowed</t>
         </is>
       </c>
-      <c r="O22" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="14">
-      <c r="A23" s="16" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E23)),ISNUMBER(SEARCH("thane",E23)),ISNUMBER(SEARCH("remote",E23))),"1 Mumbai/Remote",IF(OR(E23="",E23="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="O25" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="14">
+      <c r="A26" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E26)),ISNUMBER(SEARCH("thane",E26)),ISNUMBER(SEARCH("remote",E26))),"1 Mumbai/Remote",IF(OR(E26="",E26="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>Virtusa</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>Lead Software Engineer</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F26" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G26" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H23" s="18" t="n">
+      <c r="H26" s="28" t="n">
         <v>46305</v>
       </c>
-      <c r="I23" s="19">
-        <f>IF(H23="","",TODAY()-H23)</f>
-        <v/>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K23" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L23" s="18" t="n"/>
-      <c r="M23" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N23" s="17" t="inlineStr">
+      <c r="I26" s="29">
+        <f>IF(H26="","",TODAY()-H26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K26" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L26" s="28" t="n"/>
+      <c r="M26" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N26" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O23" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="24" ht="23.85" customHeight="1" s="14">
-      <c r="A24" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E24)),ISNUMBER(SEARCH("thane",E24)),ISNUMBER(SEARCH("remote",E24))),"1 Mumbai/Remote",IF(OR(E24="",E24="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="O26" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="14">
+      <c r="A27" s="27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E27)),ISNUMBER(SEARCH("thane",E27)),ISNUMBER(SEARCH("remote",E27))),"1 Mumbai/Remote",IF(OR(E27="",E27="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>Booking Holdings</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>Associate Software Engineer</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F27" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G27" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H24" s="18" t="n">
+      <c r="H27" s="28" t="n">
         <v>46305</v>
       </c>
-      <c r="I24" s="19">
-        <f>IF(H24="","",TODAY()-H24)</f>
-        <v/>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K24" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L24" s="18" t="n"/>
-      <c r="M24" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N24" s="17" t="inlineStr">
+      <c r="I27" s="29">
+        <f>IF(H27="","",TODAY()-H27)</f>
+        <v/>
+      </c>
+      <c r="J27" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K27" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L27" s="28" t="n"/>
+      <c r="M27" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N27" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O24" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="14">
-      <c r="A25" s="16" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E25)),ISNUMBER(SEARCH("thane",E25)),ISNUMBER(SEARCH("remote",E25))),"1 Mumbai/Remote",IF(OR(E25="",E25="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="O27" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="14">
+      <c r="A28" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E28)),ISNUMBER(SEARCH("thane",E28)),ISNUMBER(SEARCH("remote",E28))),"1 Mumbai/Remote",IF(OR(E28="",E28="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>Hdfc Securities</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>Systems Engineer, Database Services</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F28" s="27" t="inlineStr">
         <is>
           <t>5-8 yrs</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G28" s="27" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="H25" s="18" t="n">
+      <c r="H28" s="28" t="n">
         <v>46305</v>
       </c>
-      <c r="I25" s="19">
-        <f>IF(H25="","",TODAY()-H25)</f>
-        <v/>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L25" s="18" t="n"/>
-      <c r="M25" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N25" s="17" t="inlineStr">
+      <c r="I28" s="29">
+        <f>IF(H28="","",TODAY()-H28)</f>
+        <v/>
+      </c>
+      <c r="J28" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K28" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L28" s="28" t="n"/>
+      <c r="M28" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N28" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O25" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="14">
-      <c r="A26" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E26)),ISNUMBER(SEARCH("thane",E26)),ISNUMBER(SEARCH("remote",E26))),"1 Mumbai/Remote",IF(OR(E26="",E26="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="O28" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="29" ht="23.85" customHeight="1" s="14">
+      <c r="A29" s="27" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E29)),ISNUMBER(SEARCH("thane",E29)),ISNUMBER(SEARCH("remote",E29))),"1 Mumbai/Remote",IF(OR(E29="",E29="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>NEC Software Solutions</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>Senior Software Engineer - Java, Angular</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F29" s="27" t="inlineStr">
         <is>
           <t>Mid-Senior</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G29" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H26" s="18" t="n">
+      <c r="H29" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I26" s="19">
-        <f>IF(H26="","",TODAY()-H26)</f>
-        <v/>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K26" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L26" s="18" t="n"/>
-      <c r="M26" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N26" s="17" t="inlineStr">
+      <c r="I29" s="29">
+        <f>IF(H29="","",TODAY()-H29)</f>
+        <v/>
+      </c>
+      <c r="J29" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K29" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L29" s="28" t="n"/>
+      <c r="M29" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N29" s="17" t="inlineStr">
         <is>
           <t>Full-stack (Angular)</t>
         </is>
       </c>
-      <c r="O26" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="14">
-      <c r="A27" s="16" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E27)),ISNUMBER(SEARCH("thane",E27)),ISNUMBER(SEARCH("remote",E27))),"1 Mumbai/Remote",IF(OR(E27="",E27="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="O29" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="14">
+      <c r="A30" s="27" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E30)),ISNUMBER(SEARCH("thane",E30)),ISNUMBER(SEARCH("remote",E30))),"1 Mumbai/Remote",IF(OR(E30="",E30="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>Nuvama Group</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>Java Developer</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F30" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G30" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H27" s="18" t="n">
+      <c r="H30" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I27" s="19">
-        <f>IF(H27="","",TODAY()-H27)</f>
-        <v/>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K27" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L27" s="18" t="n"/>
-      <c r="M27" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N27" s="17" t="inlineStr">
+      <c r="I30" s="29">
+        <f>IF(H30="","",TODAY()-H30)</f>
+        <v/>
+      </c>
+      <c r="J30" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K30" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L30" s="28" t="n"/>
+      <c r="M30" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N30" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O27" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="14">
-      <c r="A28" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E28)),ISNUMBER(SEARCH("thane",E28)),ISNUMBER(SEARCH("remote",E28))),"1 Mumbai/Remote",IF(OR(E28="",E28="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="O30" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="14">
+      <c r="A31" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E31)),ISNUMBER(SEARCH("thane",E31)),ISNUMBER(SEARCH("remote",E31))),"1 Mumbai/Remote",IF(OR(E31="",E31="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>Tech Consulting - FS - CNS - TC - Java Developer</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F31" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G31" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H28" s="18" t="n">
+      <c r="H31" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I28" s="19">
-        <f>IF(H28="","",TODAY()-H28)</f>
-        <v/>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K28" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L28" s="18" t="n"/>
-      <c r="M28" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N28" s="17" t="inlineStr">
+      <c r="I31" s="29">
+        <f>IF(H31="","",TODAY()-H31)</f>
+        <v/>
+      </c>
+      <c r="J31" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K31" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L31" s="28" t="n"/>
+      <c r="M31" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N31" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O28" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="29" ht="23.85" customHeight="1" s="14">
-      <c r="A29" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E29)),ISNUMBER(SEARCH("thane",E29)),ISNUMBER(SEARCH("remote",E29))),"1 Mumbai/Remote",IF(OR(E29="",E29="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="O31" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="32" ht="23.85" customHeight="1" s="14">
+      <c r="A32" s="27" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E32)),ISNUMBER(SEARCH("thane",E32)),ISNUMBER(SEARCH("remote",E32))),"1 Mumbai/Remote",IF(OR(E32="",E32="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>Senior Software Engineer – Node.js &amp; TypeScript - Build from 0 to 1</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F32" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G32" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H29" s="18" t="n">
+      <c r="H32" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I29" s="19">
-        <f>IF(H29="","",TODAY()-H29)</f>
-        <v/>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K29" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L29" s="18" t="n"/>
-      <c r="M29" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N29" s="17" t="inlineStr">
+      <c r="I32" s="29">
+        <f>IF(H32="","",TODAY()-H32)</f>
+        <v/>
+      </c>
+      <c r="J32" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K32" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L32" s="28" t="n"/>
+      <c r="M32" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N32" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O29" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="14">
-      <c r="A30" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E30)),ISNUMBER(SEARCH("thane",E30)),ISNUMBER(SEARCH("remote",E30))),"1 Mumbai/Remote",IF(OR(E30="",E30="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="O32" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="14">
+      <c r="A33" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E33)),ISNUMBER(SEARCH("thane",E33)),ISNUMBER(SEARCH("remote",E33))),"1 Mumbai/Remote",IF(OR(E33="",E33="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Vastika Inc</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>Java Software Engineer</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F33" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="G33" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H30" s="18" t="n">
+      <c r="H33" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I30" s="19">
-        <f>IF(H30="","",TODAY()-H30)</f>
-        <v/>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K30" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L30" s="18" t="n"/>
-      <c r="M30" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N30" s="17" t="inlineStr">
+      <c r="I33" s="29">
+        <f>IF(H33="","",TODAY()-H33)</f>
+        <v/>
+      </c>
+      <c r="J33" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K33" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L33" s="28" t="n"/>
+      <c r="M33" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N33" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O30" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="14">
-      <c r="A31" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E31)),ISNUMBER(SEARCH("thane",E31)),ISNUMBER(SEARCH("remote",E31))),"1 Mumbai/Remote",IF(OR(E31="",E31="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="O33" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="27" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E34)),ISNUMBER(SEARCH("thane",E34)),ISNUMBER(SEARCH("remote",E34))),"1 Mumbai/Remote",IF(OR(E34="",E34="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>Mindbrain</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>Senior Java &amp; Node.js Developer</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F34" s="27" t="inlineStr">
         <is>
           <t>6-10 yrs</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G34" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H31" s="18" t="n">
+      <c r="H34" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I31" s="19">
-        <f>IF(H31="","",TODAY()-H31)</f>
-        <v/>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K31" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L31" s="18" t="n"/>
-      <c r="M31" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N31" s="17" t="inlineStr">
+      <c r="I34" s="29">
+        <f>IF(H34="","",TODAY()-H34)</f>
+        <v/>
+      </c>
+      <c r="J34" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K34" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L34" s="28" t="n"/>
+      <c r="M34" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N34" s="17" t="inlineStr">
         <is>
           <t>Stretch on experience; immediate joiners preferred</t>
         </is>
       </c>
-      <c r="O31" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="32" ht="23.85" customHeight="1" s="14">
-      <c r="A32" s="16" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E32)),ISNUMBER(SEARCH("thane",E32)),ISNUMBER(SEARCH("remote",E32))),"1 Mumbai/Remote",IF(OR(E32="",E32="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="O34" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="27" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E35)),ISNUMBER(SEARCH("thane",E35)),ISNUMBER(SEARCH("remote",E35))),"1 Mumbai/Remote",IF(OR(E35="",E35="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>Java React Software Developer - Mphasis</t>
         </is>
       </c>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F35" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="G35" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H32" s="18" t="n">
+      <c r="H35" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I32" s="19">
-        <f>IF(H32="","",TODAY()-H32)</f>
-        <v/>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K32" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L32" s="18" t="n"/>
-      <c r="M32" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N32" s="17" t="inlineStr">
+      <c r="I35" s="29">
+        <f>IF(H35="","",TODAY()-H35)</f>
+        <v/>
+      </c>
+      <c r="J35" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K35" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L35" s="28" t="n"/>
+      <c r="M35" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N35" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O32" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="14">
-      <c r="A33" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E33)),ISNUMBER(SEARCH("thane",E33)),ISNUMBER(SEARCH("remote",E33))),"1 Mumbai/Remote",IF(OR(E33="",E33="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="O35" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E36)),ISNUMBER(SEARCH("thane",E36)),ISNUMBER(SEARCH("remote",E36))),"1 Mumbai/Remote",IF(OR(E36="",E36="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>Talentgigs</t>
         </is>
       </c>
-      <c r="D33" s="17" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>Java - Fullstack Developer</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F36" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="G36" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H33" s="18" t="n">
+      <c r="H36" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I33" s="19">
-        <f>IF(H33="","",TODAY()-H33)</f>
-        <v/>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K33" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L33" s="18" t="n"/>
-      <c r="M33" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N33" s="17" t="inlineStr">
+      <c r="I36" s="29">
+        <f>IF(H36="","",TODAY()-H36)</f>
+        <v/>
+      </c>
+      <c r="J36" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K36" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L36" s="28" t="n"/>
+      <c r="M36" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N36" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O33" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="16" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E34)),ISNUMBER(SEARCH("thane",E34)),ISNUMBER(SEARCH("remote",E34))),"1 Mumbai/Remote",IF(OR(E34="",E34="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="O36" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="27" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E37)),ISNUMBER(SEARCH("thane",E37)),ISNUMBER(SEARCH("remote",E37))),"1 Mumbai/Remote",IF(OR(E37="",E37="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>Software Development Engineer III - Backend Technologies</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F37" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="G37" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H34" s="18" t="n">
+      <c r="H37" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I34" s="19">
-        <f>IF(H34="","",TODAY()-H34)</f>
-        <v/>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K34" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L34" s="18" t="n"/>
-      <c r="M34" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N34" s="17" t="inlineStr">
+      <c r="I37" s="29">
+        <f>IF(H37="","",TODAY()-H37)</f>
+        <v/>
+      </c>
+      <c r="J37" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K37" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L37" s="28" t="n"/>
+      <c r="M37" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N37" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O34" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E35)),ISNUMBER(SEARCH("thane",E35)),ISNUMBER(SEARCH("remote",E35))),"1 Mumbai/Remote",IF(OR(E35="",E35="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="O37" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E38)),ISNUMBER(SEARCH("thane",E38)),ISNUMBER(SEARCH("remote",E38))),"1 Mumbai/Remote",IF(OR(E38="",E38="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>Sr. Java Full Stack Developer(Angular) – India - Remote</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F38" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="G38" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H35" s="18" t="n">
+      <c r="H38" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I35" s="19">
-        <f>IF(H35="","",TODAY()-H35)</f>
-        <v/>
-      </c>
-      <c r="J35" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K35" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L35" s="18" t="n"/>
-      <c r="M35" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N35" s="17" t="inlineStr">
+      <c r="I38" s="29">
+        <f>IF(H38="","",TODAY()-H38)</f>
+        <v/>
+      </c>
+      <c r="J38" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K38" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L38" s="28" t="n"/>
+      <c r="M38" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N38" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O35" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E36)),ISNUMBER(SEARCH("thane",E36)),ISNUMBER(SEARCH("remote",E36))),"1 Mumbai/Remote",IF(OR(E36="",E36="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
+      <c r="O38" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="27" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E39)),ISNUMBER(SEARCH("thane",E39)),ISNUMBER(SEARCH("remote",E39))),"1 Mumbai/Remote",IF(OR(E39="",E39="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>Smartstream</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>SMSTR85 - Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="G39" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H39" s="28" t="n">
+        <v>46303</v>
+      </c>
+      <c r="I39" s="29">
+        <f>IF(H39="","",TODAY()-H39)</f>
+        <v/>
+      </c>
+      <c r="J39" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K39" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L39" s="28" t="n"/>
+      <c r="M39" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N39" s="17" t="inlineStr">
+        <is>
+          <t>Auto-added; check company/location</t>
+        </is>
+      </c>
+      <c r="O39" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="27" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E40)),ISNUMBER(SEARCH("thane",E40)),ISNUMBER(SEARCH("remote",E40))),"1 Mumbai/Remote",IF(OR(E40="",E40="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>Mphasis</t>
         </is>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>Java Software Engineer</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F40" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="G40" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H36" s="18" t="n">
+      <c r="H40" s="28" t="n">
         <v>46302</v>
       </c>
-      <c r="I36" s="19">
-        <f>IF(H36="","",TODAY()-H36)</f>
-        <v/>
-      </c>
-      <c r="J36" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K36" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L36" s="18" t="n"/>
-      <c r="M36" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N36" s="17" t="inlineStr">
+      <c r="I40" s="29">
+        <f>IF(H40="","",TODAY()-H40)</f>
+        <v/>
+      </c>
+      <c r="J40" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K40" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L40" s="28" t="n"/>
+      <c r="M40" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N40" s="17" t="inlineStr">
         <is>
           <t>At the 7-day edge</t>
         </is>
       </c>
-      <c r="O36" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="16" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E37)),ISNUMBER(SEARCH("thane",E37)),ISNUMBER(SEARCH("remote",E37))),"1 Mumbai/Remote",IF(OR(E37="",E37="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
+      <c r="O40" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E41)),ISNUMBER(SEARCH("thane",E41)),ISNUMBER(SEARCH("remote",E41))),"1 Mumbai/Remote",IF(OR(E41="",E41="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D37" s="17" t="inlineStr">
+      <c r="D41" s="17" t="inlineStr">
         <is>
           <t>Backend Java Developer (100% Remote/Work From Home)</t>
         </is>
       </c>
-      <c r="E37" s="17" t="inlineStr">
+      <c r="E41" s="17" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F41" s="27" t="inlineStr">
         <is>
           <t>4-7 yrs</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="G41" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H37" s="18" t="n">
+      <c r="H41" s="28" t="n">
         <v>46302</v>
       </c>
-      <c r="I37" s="19">
-        <f>IF(H37="","",TODAY()-H37)</f>
-        <v/>
-      </c>
-      <c r="J37" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K37" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L37" s="18" t="n"/>
-      <c r="M37" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N37" s="17" t="inlineStr">
+      <c r="I41" s="29">
+        <f>IF(H41="","",TODAY()-H41)</f>
+        <v/>
+      </c>
+      <c r="J41" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K41" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L41" s="28" t="n"/>
+      <c r="M41" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N41" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O37" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="16" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E38)),ISNUMBER(SEARCH("thane",E38)),ISNUMBER(SEARCH("remote",E38))),"1 Mumbai/Remote",IF(OR(E38="",E38="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C38" s="17" t="inlineStr">
+      <c r="O41" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E42)),ISNUMBER(SEARCH("thane",E42)),ISNUMBER(SEARCH("remote",E42))),"1 Mumbai/Remote",IF(OR(E42="",E42="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
         <is>
           <t>Uplers</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D42" s="17" t="inlineStr">
         <is>
           <t>Backend Developer (Java / Spring)</t>
         </is>
       </c>
-      <c r="E38" s="17" t="inlineStr">
+      <c r="E42" s="17" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="F42" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G38" s="16" t="inlineStr">
+      <c r="G42" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H38" s="18" t="n">
+      <c r="H42" s="28" t="n">
         <v>46302</v>
       </c>
-      <c r="I38" s="19">
-        <f>IF(H38="","",TODAY()-H38)</f>
-        <v/>
-      </c>
-      <c r="J38" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K38" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L38" s="18" t="n"/>
-      <c r="M38" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N38" s="17" t="inlineStr">
+      <c r="I42" s="29">
+        <f>IF(H42="","",TODAY()-H42)</f>
+        <v/>
+      </c>
+      <c r="J42" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K42" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L42" s="28" t="n"/>
+      <c r="M42" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N42" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O38" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="16" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E39)),ISNUMBER(SEARCH("thane",E39)),ISNUMBER(SEARCH("remote",E39))),"1 Mumbai/Remote",IF(OR(E39="",E39="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C39" s="17" t="inlineStr">
+      <c r="O42" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="27" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E43)),ISNUMBER(SEARCH("thane",E43)),ISNUMBER(SEARCH("remote",E43))),"1 Mumbai/Remote",IF(OR(E43="",E43="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
         <is>
           <t>Naukri (company not shown)</t>
         </is>
       </c>
-      <c r="D39" s="17" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>Java Spring Boot Developer</t>
         </is>
       </c>
-      <c r="E39" s="17" t="inlineStr">
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>Mumbai / Thane / Navi Mumbai</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr">
+      <c r="F43" s="27" t="inlineStr">
         <is>
           <t>2-6 yrs</t>
         </is>
       </c>
-      <c r="G39" s="16" t="inlineStr">
+      <c r="G43" s="27" t="inlineStr">
         <is>
           <t>Naukri</t>
         </is>
       </c>
-      <c r="H39" s="18" t="n">
+      <c r="H43" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I39" s="19">
-        <f>IF(H39="","",TODAY()-H39)</f>
-        <v/>
-      </c>
-      <c r="J39" s="16" t="inlineStr">
+      <c r="I43" s="29">
+        <f>IF(H43="","",TODAY()-H43)</f>
+        <v/>
+      </c>
+      <c r="J43" s="27" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K39" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L39" s="18" t="n"/>
-      <c r="M39" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N39" s="17" t="inlineStr">
+      <c r="K43" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L43" s="28" t="n"/>
+      <c r="M43" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N43" s="17" t="inlineStr">
         <is>
           <t>Junior-leaning band</t>
         </is>
       </c>
-      <c r="O39" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="16" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E40)),ISNUMBER(SEARCH("thane",E40)),ISNUMBER(SEARCH("remote",E40))),"1 Mumbai/Remote",IF(OR(E40="",E40="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C40" s="17" t="inlineStr">
+      <c r="O43" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="27" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E44)),ISNUMBER(SEARCH("thane",E44)),ISNUMBER(SEARCH("remote",E44))),"1 Mumbai/Remote",IF(OR(E44="",E44="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
         <is>
           <t>Nium</t>
         </is>
       </c>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="D44" s="17" t="inlineStr">
         <is>
           <t>SDE II - Java Backend: Issuance</t>
         </is>
       </c>
-      <c r="E40" s="17" t="inlineStr">
+      <c r="E44" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="F44" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G40" s="16" t="inlineStr">
+      <c r="G44" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H40" s="18" t="n">
+      <c r="H44" s="28" t="n">
         <v>46308</v>
       </c>
-      <c r="I40" s="19">
-        <f>IF(H40="","",TODAY()-H40)</f>
-        <v/>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
+      <c r="I44" s="29">
+        <f>IF(H44="","",TODAY()-H44)</f>
+        <v/>
+      </c>
+      <c r="J44" s="27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K40" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L40" s="18" t="n"/>
-      <c r="M40" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N40" s="17" t="inlineStr">
+      <c r="K44" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L44" s="28" t="n"/>
+      <c r="M44" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N44" s="17" t="inlineStr">
         <is>
           <t>Fintech; posted ~24h ago. Confirm location</t>
         </is>
       </c>
-      <c r="O40" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E41)),ISNUMBER(SEARCH("thane",E41)),ISNUMBER(SEARCH("remote",E41))),"1 Mumbai/Remote",IF(OR(E41="",E41="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
+      <c r="O44" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="27" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E45)),ISNUMBER(SEARCH("thane",E45)),ISNUMBER(SEARCH("remote",E45))),"1 Mumbai/Remote",IF(OR(E45="",E45="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D41" s="17" t="inlineStr">
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>Java Full Stack Developer – Spring Boot, Microservices, Kafka, AWS ...</t>
         </is>
       </c>
-      <c r="E41" s="17" t="inlineStr">
+      <c r="E45" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F41" s="16" t="inlineStr">
+      <c r="F45" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G41" s="16" t="inlineStr">
+      <c r="G45" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H41" s="18" t="n">
+      <c r="H45" s="28" t="n">
         <v>46306</v>
       </c>
-      <c r="I41" s="19">
-        <f>IF(H41="","",TODAY()-H41)</f>
-        <v/>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
+      <c r="I45" s="29">
+        <f>IF(H45="","",TODAY()-H45)</f>
+        <v/>
+      </c>
+      <c r="J45" s="27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K41" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L41" s="18" t="n"/>
-      <c r="M41" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N41" s="17" t="inlineStr">
+      <c r="K45" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L45" s="28" t="n"/>
+      <c r="M45" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N45" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O41" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="16" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E42)),ISNUMBER(SEARCH("thane",E42)),ISNUMBER(SEARCH("remote",E42))),"1 Mumbai/Remote",IF(OR(E42="",E42="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
+      <c r="O45" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E46)),ISNUMBER(SEARCH("thane",E46)),ISNUMBER(SEARCH("remote",E46))),"1 Mumbai/Remote",IF(OR(E46="",E46="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>Java Backend Developer | Microservices | Spring Security | JWT</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F42" s="16" t="inlineStr">
+      <c r="F46" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G42" s="16" t="inlineStr">
+      <c r="G46" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H42" s="18" t="n">
+      <c r="H46" s="28" t="n">
         <v>46306</v>
       </c>
-      <c r="I42" s="19">
-        <f>IF(H42="","",TODAY()-H42)</f>
-        <v/>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
+      <c r="I46" s="29">
+        <f>IF(H46="","",TODAY()-H46)</f>
+        <v/>
+      </c>
+      <c r="J46" s="27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K42" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L42" s="18" t="n"/>
-      <c r="M42" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N42" s="17" t="inlineStr">
+      <c r="K46" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L46" s="28" t="n"/>
+      <c r="M46" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N46" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O42" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="16" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E43)),ISNUMBER(SEARCH("thane",E43)),ISNUMBER(SEARCH("remote",E43))),"1 Mumbai/Remote",IF(OR(E43="",E43="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
+      <c r="O46" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="27" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E47)),ISNUMBER(SEARCH("thane",E47)),ISNUMBER(SEARCH("remote",E47))),"1 Mumbai/Remote",IF(OR(E47="",E47="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
         <is>
           <t>WillWare Technologies</t>
         </is>
       </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="D47" s="17" t="inlineStr">
         <is>
           <t>Java Microservices Developer (GCP)</t>
         </is>
       </c>
-      <c r="E43" s="17" t="inlineStr">
+      <c r="E47" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F43" s="16" t="inlineStr">
+      <c r="F47" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G43" s="16" t="inlineStr">
+      <c r="G47" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H43" s="18" t="n">
+      <c r="H47" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I43" s="19">
-        <f>IF(H43="","",TODAY()-H43)</f>
-        <v/>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
+      <c r="I47" s="29">
+        <f>IF(H47="","",TODAY()-H47)</f>
+        <v/>
+      </c>
+      <c r="J47" s="27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K43" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L43" s="18" t="n"/>
-      <c r="M43" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N43" s="17" t="inlineStr">
+      <c r="K47" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L47" s="28" t="n"/>
+      <c r="M47" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N47" s="17" t="inlineStr">
         <is>
           <t>Java, Spring Boot, Kafka, GCP. Confirm location</t>
         </is>
       </c>
-      <c r="O43" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="16" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E44)),ISNUMBER(SEARCH("thane",E44)),ISNUMBER(SEARCH("remote",E44))),"1 Mumbai/Remote",IF(OR(E44="",E44="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C44" s="17" t="inlineStr">
+      <c r="O47" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="27" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E48)),ISNUMBER(SEARCH("thane",E48)),ISNUMBER(SEARCH("remote",E48))),"1 Mumbai/Remote",IF(OR(E48="",E48="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="D48" s="17" t="inlineStr">
         <is>
           <t>Senior Full Stack Engineer - Java Backend &amp; Kafka</t>
         </is>
       </c>
-      <c r="E44" s="17" t="inlineStr">
+      <c r="E48" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F44" s="16" t="inlineStr">
+      <c r="F48" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G44" s="16" t="inlineStr">
+      <c r="G48" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H44" s="18" t="n">
-        <v>46309</v>
-      </c>
-      <c r="I44" s="19">
-        <f>IF(H44="","",TODAY()-H44)</f>
-        <v/>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K44" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L44" s="18" t="n"/>
-      <c r="M44" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N44" s="17" t="inlineStr">
+      <c r="H48" s="28" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I48" s="29">
+        <f>IF(H48="","",TODAY()-H48)</f>
+        <v/>
+      </c>
+      <c r="J48" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K48" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L48" s="28" t="n"/>
+      <c r="M48" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N48" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O44" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="16" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E45)),ISNUMBER(SEARCH("thane",E45)),ISNUMBER(SEARCH("remote",E45))),"1 Mumbai/Remote",IF(OR(E45="",E45="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C45" s="17" t="inlineStr">
+      <c r="O48" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="27" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E49)),ISNUMBER(SEARCH("thane",E49)),ISNUMBER(SEARCH("remote",E49))),"1 Mumbai/Remote",IF(OR(E49="",E49="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>See link</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="inlineStr">
+        <is>
+          <t>Full Stack Developer (Angular, Java, Spring Boot, AWS, AI Tools)</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="F49" s="27" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="G49" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H49" s="28" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I49" s="29">
+        <f>IF(H49="","",TODAY()-H49)</f>
+        <v/>
+      </c>
+      <c r="J49" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K49" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L49" s="28" t="n"/>
+      <c r="M49" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N49" s="17" t="inlineStr">
+        <is>
+          <t>Auto-added; check company/location</t>
+        </is>
+      </c>
+      <c r="O49" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E50)),ISNUMBER(SEARCH("thane",E50)),ISNUMBER(SEARCH("remote",E50))),"1 Mumbai/Remote",IF(OR(E50="",E50="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>See link</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase Software Engineer Salary | $114K-$632K+ | Levels.fyi</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="F50" s="27" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="G50" s="27" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H50" s="28" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I50" s="29">
+        <f>IF(H50="","",TODAY()-H50)</f>
+        <v/>
+      </c>
+      <c r="J50" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K50" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L50" s="28" t="n"/>
+      <c r="M50" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N50" s="17" t="inlineStr">
+        <is>
+          <t>Auto-added; check company/location</t>
+        </is>
+      </c>
+      <c r="O50" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E51)),ISNUMBER(SEARCH("thane",E51)),ISNUMBER(SEARCH("remote",E51))),"1 Mumbai/Remote",IF(OR(E51="",E51="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>IPS Vantage Tech Services Pvt. Limited</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>Lead Java Developer</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="F51" s="27" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="G51" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H51" s="28" t="n">
+        <v>46308</v>
+      </c>
+      <c r="I51" s="29">
+        <f>IF(H51="","",TODAY()-H51)</f>
+        <v/>
+      </c>
+      <c r="J51" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K51" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L51" s="28" t="n"/>
+      <c r="M51" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N51" s="17" t="inlineStr">
+        <is>
+          <t>Auto-added; check company/location</t>
+        </is>
+      </c>
+      <c r="O51" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="27" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E52)),ISNUMBER(SEARCH("thane",E52)),ISNUMBER(SEARCH("remote",E52))),"1 Mumbai/Remote",IF(OR(E52="",E52="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>See link</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>Fiserv hiring Advisor, Software Development Engineering(Java ...</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="F52" s="27" t="inlineStr">
+        <is>
+          <t>5+ yrs</t>
+        </is>
+      </c>
+      <c r="G52" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H52" s="28" t="n">
+        <v>46308</v>
+      </c>
+      <c r="I52" s="29">
+        <f>IF(H52="","",TODAY()-H52)</f>
+        <v/>
+      </c>
+      <c r="J52" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K52" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L52" s="28" t="n"/>
+      <c r="M52" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N52" s="17" t="inlineStr">
+        <is>
+          <t>Auto-added; check company/location</t>
+        </is>
+      </c>
+      <c r="O52" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="27" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E53)),ISNUMBER(SEARCH("thane",E53)),ISNUMBER(SEARCH("remote",E53))),"1 Mumbai/Remote",IF(OR(E53="",E53="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
         <is>
           <t>Mastercard</t>
         </is>
       </c>
-      <c r="D45" s="17" t="inlineStr">
+      <c r="D53" s="17" t="inlineStr">
         <is>
           <t>Senior Full-Stack Engineer - React, TypeScript, Node, Java</t>
         </is>
       </c>
-      <c r="E45" s="17" t="inlineStr">
+      <c r="E53" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F45" s="16" t="inlineStr">
+      <c r="F53" s="27" t="inlineStr">
         <is>
           <t>5+ yrs</t>
         </is>
       </c>
-      <c r="G45" s="16" t="inlineStr">
+      <c r="G53" s="27" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="H45" s="18" t="n">
+      <c r="H53" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="I45" s="19">
-        <f>IF(H45="","",TODAY()-H45)</f>
-        <v/>
-      </c>
-      <c r="J45" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K45" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L45" s="18" t="n"/>
-      <c r="M45" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N45" s="17" t="inlineStr">
+      <c r="I53" s="29">
+        <f>IF(H53="","",TODAY()-H53)</f>
+        <v/>
+      </c>
+      <c r="J53" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K53" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L53" s="28" t="n"/>
+      <c r="M53" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N53" s="17" t="inlineStr">
         <is>
           <t>Matches your React/Node/Java mix. Confirm location</t>
         </is>
       </c>
-      <c r="O45" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E46)),ISNUMBER(SEARCH("thane",E46)),ISNUMBER(SEARCH("remote",E46))),"1 Mumbai/Remote",IF(OR(E46="",E46="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C46" s="17" t="inlineStr">
+      <c r="O53" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="27" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E54)),ISNUMBER(SEARCH("thane",E54)),ISNUMBER(SEARCH("remote",E54))),"1 Mumbai/Remote",IF(OR(E54="",E54="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
         <is>
           <t>Finlabs India</t>
         </is>
       </c>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="D54" s="17" t="inlineStr">
         <is>
           <t>Senior Java Developer</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
+      <c r="E54" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F46" s="16" t="inlineStr">
+      <c r="F54" s="27" t="inlineStr">
         <is>
           <t>3-5 yrs</t>
         </is>
       </c>
-      <c r="G46" s="16" t="inlineStr">
+      <c r="G54" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H46" s="18" t="n">
+      <c r="H54" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="I46" s="19">
-        <f>IF(H46="","",TODAY()-H46)</f>
-        <v/>
-      </c>
-      <c r="J46" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K46" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L46" s="18" t="n"/>
-      <c r="M46" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N46" s="17" t="inlineStr">
+      <c r="I54" s="29">
+        <f>IF(H54="","",TODAY()-H54)</f>
+        <v/>
+      </c>
+      <c r="J54" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K54" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L54" s="28" t="n"/>
+      <c r="M54" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N54" s="17" t="inlineStr">
         <is>
           <t>Confirm location</t>
         </is>
       </c>
-      <c r="O46" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E47)),ISNUMBER(SEARCH("thane",E47)),ISNUMBER(SEARCH("remote",E47))),"1 Mumbai/Remote",IF(OR(E47="",E47="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C47" s="17" t="inlineStr">
+      <c r="O54" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="27" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E55)),ISNUMBER(SEARCH("thane",E55)),ISNUMBER(SEARCH("remote",E55))),"1 Mumbai/Remote",IF(OR(E55="",E55="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
         <is>
           <t>Flexton Inc.</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D55" s="17" t="inlineStr">
         <is>
           <t>Senior Java Backend Engineer (Prosper migration)</t>
         </is>
       </c>
-      <c r="E47" s="17" t="inlineStr">
+      <c r="E55" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F47" s="16" t="inlineStr">
+      <c r="F55" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G47" s="16" t="inlineStr">
+      <c r="G55" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H47" s="18" t="n">
+      <c r="H55" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="I47" s="19">
-        <f>IF(H47="","",TODAY()-H47)</f>
-        <v/>
-      </c>
-      <c r="J47" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K47" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L47" s="18" t="n"/>
-      <c r="M47" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N47" s="17" t="inlineStr">
+      <c r="I55" s="29">
+        <f>IF(H55="","",TODAY()-H55)</f>
+        <v/>
+      </c>
+      <c r="J55" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K55" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L55" s="28" t="n"/>
+      <c r="M55" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N55" s="17" t="inlineStr">
         <is>
           <t>Listed as India; confirm city/remote</t>
         </is>
       </c>
-      <c r="O47" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="16" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E48)),ISNUMBER(SEARCH("thane",E48)),ISNUMBER(SEARCH("remote",E48))),"1 Mumbai/Remote",IF(OR(E48="",E48="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C48" s="17" t="inlineStr">
+      <c r="O55" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="27" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E56)),ISNUMBER(SEARCH("thane",E56)),ISNUMBER(SEARCH("remote",E56))),"1 Mumbai/Remote",IF(OR(E56="",E56="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="D56" s="17" t="inlineStr">
         <is>
           <t>Software Engineer III - Java, AWS, Kafka</t>
         </is>
       </c>
-      <c r="E48" s="17" t="inlineStr">
+      <c r="E56" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F48" s="16" t="inlineStr">
+      <c r="F56" s="27" t="inlineStr">
         <is>
           <t>3+ yrs</t>
         </is>
       </c>
-      <c r="G48" s="16" t="inlineStr">
+      <c r="G56" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H48" s="18" t="n">
+      <c r="H56" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="I48" s="19">
-        <f>IF(H48="","",TODAY()-H48)</f>
-        <v/>
-      </c>
-      <c r="J48" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K48" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L48" s="18" t="n"/>
-      <c r="M48" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N48" s="17" t="inlineStr">
+      <c r="I56" s="29">
+        <f>IF(H56="","",TODAY()-H56)</f>
+        <v/>
+      </c>
+      <c r="J56" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K56" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L56" s="28" t="n"/>
+      <c r="M56" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N56" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O48" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="16" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E49)),ISNUMBER(SEARCH("thane",E49)),ISNUMBER(SEARCH("remote",E49))),"1 Mumbai/Remote",IF(OR(E49="",E49="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
+      <c r="O56" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="27" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E57)),ISNUMBER(SEARCH("thane",E57)),ISNUMBER(SEARCH("remote",E57))),"1 Mumbai/Remote",IF(OR(E57="",E57="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D49" s="17" t="inlineStr">
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>TIS/ Java Developer (Kafka and Containerization)</t>
         </is>
       </c>
-      <c r="E49" s="17" t="inlineStr">
+      <c r="E57" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F49" s="16" t="inlineStr">
+      <c r="F57" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G49" s="16" t="inlineStr">
+      <c r="G57" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H49" s="18" t="n">
+      <c r="H57" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="I49" s="19">
-        <f>IF(H49="","",TODAY()-H49)</f>
-        <v/>
-      </c>
-      <c r="J49" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K49" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L49" s="18" t="n"/>
-      <c r="M49" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N49" s="17" t="inlineStr">
+      <c r="I57" s="29">
+        <f>IF(H57="","",TODAY()-H57)</f>
+        <v/>
+      </c>
+      <c r="J57" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K57" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L57" s="28" t="n"/>
+      <c r="M57" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N57" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O49" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="16" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E50)),ISNUMBER(SEARCH("thane",E50)),ISNUMBER(SEARCH("remote",E50))),"1 Mumbai/Remote",IF(OR(E50="",E50="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C50" s="17" t="inlineStr">
+      <c r="O57" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="27" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E58)),ISNUMBER(SEARCH("thane",E58)),ISNUMBER(SEARCH("remote",E58))),"1 Mumbai/Remote",IF(OR(E58="",E58="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>Lacento Technologies Private Limited</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>Java Developer</t>
+        </is>
+      </c>
+      <c r="E58" s="17" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="F58" s="27" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="G58" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H58" s="28" t="n">
+        <v>46307</v>
+      </c>
+      <c r="I58" s="29">
+        <f>IF(H58="","",TODAY()-H58)</f>
+        <v/>
+      </c>
+      <c r="J58" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K58" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L58" s="28" t="n"/>
+      <c r="M58" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N58" s="17" t="inlineStr">
+        <is>
+          <t>Auto-added; check company/location</t>
+        </is>
+      </c>
+      <c r="O58" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="27" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E59)),ISNUMBER(SEARCH("thane",E59)),ISNUMBER(SEARCH("remote",E59))),"1 Mumbai/Remote",IF(OR(E59="",E59="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
         <is>
           <t>Finlabs India Pvt Ltd</t>
         </is>
       </c>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>Senior Java Developer (3–5 Years Experience)</t>
         </is>
       </c>
-      <c r="E50" s="17" t="inlineStr">
+      <c r="E59" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F50" s="16" t="inlineStr">
+      <c r="F59" s="27" t="inlineStr">
         <is>
           <t>3-5 yrs</t>
         </is>
       </c>
-      <c r="G50" s="16" t="inlineStr">
+      <c r="G59" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H50" s="18" t="n">
+      <c r="H59" s="28" t="n">
         <v>46306</v>
       </c>
-      <c r="I50" s="19">
-        <f>IF(H50="","",TODAY()-H50)</f>
-        <v/>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K50" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L50" s="18" t="n"/>
-      <c r="M50" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N50" s="17" t="inlineStr">
+      <c r="I59" s="29">
+        <f>IF(H59="","",TODAY()-H59)</f>
+        <v/>
+      </c>
+      <c r="J59" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K59" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L59" s="28" t="n"/>
+      <c r="M59" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N59" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O50" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E51)),ISNUMBER(SEARCH("thane",E51)),ISNUMBER(SEARCH("remote",E51))),"1 Mumbai/Remote",IF(OR(E51="",E51="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C51" s="17" t="inlineStr">
+      <c r="O59" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="27" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E60)),ISNUMBER(SEARCH("thane",E60)),ISNUMBER(SEARCH("remote",E60))),"1 Mumbai/Remote",IF(OR(E60="",E60="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D51" s="17" t="inlineStr">
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>Hire the Best PostgreSQL Developers &amp; DBAs in India - Upwork</t>
         </is>
       </c>
-      <c r="E51" s="17" t="inlineStr">
+      <c r="E60" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F51" s="16" t="inlineStr">
+      <c r="F60" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G51" s="16" t="inlineStr">
+      <c r="G60" s="27" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="H51" s="18" t="n">
+      <c r="H60" s="28" t="n">
         <v>46305</v>
       </c>
-      <c r="I51" s="19">
-        <f>IF(H51="","",TODAY()-H51)</f>
-        <v/>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K51" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L51" s="18" t="n"/>
-      <c r="M51" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N51" s="17" t="inlineStr">
+      <c r="I60" s="29">
+        <f>IF(H60="","",TODAY()-H60)</f>
+        <v/>
+      </c>
+      <c r="J60" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K60" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L60" s="28" t="n"/>
+      <c r="M60" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N60" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O51" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="16" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E52)),ISNUMBER(SEARCH("thane",E52)),ISNUMBER(SEARCH("remote",E52))),"1 Mumbai/Remote",IF(OR(E52="",E52="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
+      <c r="O60" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E61)),ISNUMBER(SEARCH("thane",E61)),ISNUMBER(SEARCH("remote",E61))),"1 Mumbai/Remote",IF(OR(E61="",E61="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C61" s="17" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="D52" s="17" t="inlineStr">
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>Software Engineer - Java, Springboot, SAAS</t>
         </is>
       </c>
-      <c r="E52" s="17" t="inlineStr">
+      <c r="E61" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F52" s="16" t="inlineStr">
+      <c r="F61" s="27" t="inlineStr">
         <is>
           <t>3-6 yrs</t>
         </is>
       </c>
-      <c r="G52" s="16" t="inlineStr">
+      <c r="G61" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H52" s="18" t="n">
+      <c r="H61" s="28" t="n">
         <v>46305</v>
       </c>
-      <c r="I52" s="19">
-        <f>IF(H52="","",TODAY()-H52)</f>
-        <v/>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K52" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L52" s="18" t="n"/>
-      <c r="M52" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N52" s="17" t="inlineStr">
+      <c r="I61" s="29">
+        <f>IF(H61="","",TODAY()-H61)</f>
+        <v/>
+      </c>
+      <c r="J61" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K61" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L61" s="28" t="n"/>
+      <c r="M61" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N61" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O52" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="16" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E53)),ISNUMBER(SEARCH("thane",E53)),ISNUMBER(SEARCH("remote",E53))),"1 Mumbai/Remote",IF(OR(E53="",E53="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
+      <c r="O61" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="27" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E62)),ISNUMBER(SEARCH("thane",E62)),ISNUMBER(SEARCH("remote",E62))),"1 Mumbai/Remote",IF(OR(E62="",E62="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>JustHr hiring Senior Backend Engineer | Java, Spring Boot</t>
         </is>
       </c>
-      <c r="E53" s="17" t="inlineStr">
+      <c r="E62" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F53" s="16" t="inlineStr">
+      <c r="F62" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G53" s="16" t="inlineStr">
+      <c r="G62" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H53" s="18" t="n">
+      <c r="H62" s="28" t="n">
         <v>46305</v>
       </c>
-      <c r="I53" s="19">
-        <f>IF(H53="","",TODAY()-H53)</f>
-        <v/>
-      </c>
-      <c r="J53" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K53" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L53" s="18" t="n"/>
-      <c r="M53" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N53" s="17" t="inlineStr">
+      <c r="I62" s="29">
+        <f>IF(H62="","",TODAY()-H62)</f>
+        <v/>
+      </c>
+      <c r="J62" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K62" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L62" s="28" t="n"/>
+      <c r="M62" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N62" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O53" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="16" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E54)),ISNUMBER(SEARCH("thane",E54)),ISNUMBER(SEARCH("remote",E54))),"1 Mumbai/Remote",IF(OR(E54="",E54="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
+      <c r="O62" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="27" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E63)),ISNUMBER(SEARCH("thane",E63)),ISNUMBER(SEARCH("remote",E63))),"1 Mumbai/Remote",IF(OR(E63="",E63="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
         <is>
           <t>Mastercard</t>
         </is>
       </c>
-      <c r="D54" s="17" t="inlineStr">
+      <c r="D63" s="17" t="inlineStr">
         <is>
           <t>Software Engineer II</t>
         </is>
       </c>
-      <c r="E54" s="17" t="inlineStr">
+      <c r="E63" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F54" s="16" t="inlineStr">
+      <c r="F63" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G54" s="16" t="inlineStr">
+      <c r="G63" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H54" s="18" t="n">
+      <c r="H63" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I54" s="19">
-        <f>IF(H54="","",TODAY()-H54)</f>
-        <v/>
-      </c>
-      <c r="J54" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K54" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L54" s="18" t="n"/>
-      <c r="M54" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N54" s="17" t="inlineStr">
+      <c r="I63" s="29">
+        <f>IF(H63="","",TODAY()-H63)</f>
+        <v/>
+      </c>
+      <c r="J63" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K63" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L63" s="28" t="n"/>
+      <c r="M63" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N63" s="17" t="inlineStr">
         <is>
           <t>Confirm location and stack</t>
         </is>
       </c>
-      <c r="O54" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="16" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E55)),ISNUMBER(SEARCH("thane",E55)),ISNUMBER(SEARCH("remote",E55))),"1 Mumbai/Remote",IF(OR(E55="",E55="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C55" s="17" t="inlineStr">
+      <c r="O63" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="27" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E64)),ISNUMBER(SEARCH("thane",E64)),ISNUMBER(SEARCH("remote",E64))),"1 Mumbai/Remote",IF(OR(E64="",E64="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
         <is>
           <t>Vastika Inc</t>
         </is>
       </c>
-      <c r="D55" s="17" t="inlineStr">
+      <c r="D64" s="17" t="inlineStr">
         <is>
           <t>Senior Java Software Engineer</t>
         </is>
       </c>
-      <c r="E55" s="17" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F55" s="16" t="inlineStr">
+      <c r="F64" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G55" s="16" t="inlineStr">
+      <c r="G64" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H55" s="18" t="n">
+      <c r="H64" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I55" s="19">
-        <f>IF(H55="","",TODAY()-H55)</f>
-        <v/>
-      </c>
-      <c r="J55" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K55" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L55" s="18" t="n"/>
-      <c r="M55" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N55" s="17" t="inlineStr">
+      <c r="I64" s="29">
+        <f>IF(H64="","",TODAY()-H64)</f>
+        <v/>
+      </c>
+      <c r="J64" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K64" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L64" s="28" t="n"/>
+      <c r="M64" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N64" s="17" t="inlineStr">
         <is>
           <t>Confirm location</t>
         </is>
       </c>
-      <c r="O55" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="16" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E56)),ISNUMBER(SEARCH("thane",E56)),ISNUMBER(SEARCH("remote",E56))),"1 Mumbai/Remote",IF(OR(E56="",E56="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C56" s="17" t="inlineStr">
+      <c r="O64" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="27" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E65)),ISNUMBER(SEARCH("thane",E65)),ISNUMBER(SEARCH("remote",E65))),"1 Mumbai/Remote",IF(OR(E65="",E65="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
         <is>
           <t>InfoBeans</t>
         </is>
       </c>
-      <c r="D56" s="17" t="inlineStr">
+      <c r="D65" s="17" t="inlineStr">
         <is>
           <t>Senior Java Backend Developer</t>
         </is>
       </c>
-      <c r="E56" s="17" t="inlineStr">
+      <c r="E65" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F56" s="16" t="inlineStr">
+      <c r="F65" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G56" s="16" t="inlineStr">
+      <c r="G65" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H56" s="18" t="n">
+      <c r="H65" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I56" s="19">
-        <f>IF(H56="","",TODAY()-H56)</f>
-        <v/>
-      </c>
-      <c r="J56" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K56" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L56" s="18" t="n"/>
-      <c r="M56" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N56" s="17" t="inlineStr">
+      <c r="I65" s="29">
+        <f>IF(H65="","",TODAY()-H65)</f>
+        <v/>
+      </c>
+      <c r="J65" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K65" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L65" s="28" t="n"/>
+      <c r="M65" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N65" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O56" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="16" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E57)),ISNUMBER(SEARCH("thane",E57)),ISNUMBER(SEARCH("remote",E57))),"1 Mumbai/Remote",IF(OR(E57="",E57="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C57" s="17" t="inlineStr">
+      <c r="O65" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="27" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E66)),ISNUMBER(SEARCH("thane",E66)),ISNUMBER(SEARCH("remote",E66))),"1 Mumbai/Remote",IF(OR(E66="",E66="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
         <is>
           <t>Talent21</t>
         </is>
       </c>
-      <c r="D57" s="17" t="inlineStr">
+      <c r="D66" s="17" t="inlineStr">
         <is>
           <t>Java Developer with Drools</t>
         </is>
       </c>
-      <c r="E57" s="17" t="inlineStr">
+      <c r="E66" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F57" s="16" t="inlineStr">
+      <c r="F66" s="27" t="inlineStr">
         <is>
           <t>6-8 yrs</t>
         </is>
       </c>
-      <c r="G57" s="16" t="inlineStr">
+      <c r="G66" s="27" t="inlineStr">
         <is>
           <t>Naukri</t>
         </is>
       </c>
-      <c r="H57" s="18" t="n">
+      <c r="H66" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I57" s="19">
-        <f>IF(H57="","",TODAY()-H57)</f>
-        <v/>
-      </c>
-      <c r="J57" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K57" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L57" s="18" t="n"/>
-      <c r="M57" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N57" s="17" t="inlineStr">
+      <c r="I66" s="29">
+        <f>IF(H66="","",TODAY()-H66)</f>
+        <v/>
+      </c>
+      <c r="J66" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K66" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L66" s="28" t="n"/>
+      <c r="M66" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N66" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O57" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="16" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E58)),ISNUMBER(SEARCH("thane",E58)),ISNUMBER(SEARCH("remote",E58))),"1 Mumbai/Remote",IF(OR(E58="",E58="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C58" s="17" t="inlineStr">
+      <c r="O66" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="27" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E67)),ISNUMBER(SEARCH("thane",E67)),ISNUMBER(SEARCH("remote",E67))),"1 Mumbai/Remote",IF(OR(E67="",E67="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
         <is>
           <t>BCforward</t>
         </is>
       </c>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="D67" s="17" t="inlineStr">
         <is>
           <t>Backend Java Developer</t>
         </is>
       </c>
-      <c r="E58" s="17" t="inlineStr">
+      <c r="E67" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F58" s="16" t="inlineStr">
+      <c r="F67" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G58" s="16" t="inlineStr">
+      <c r="G67" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H58" s="18" t="n">
+      <c r="H67" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I58" s="19">
-        <f>IF(H58="","",TODAY()-H58)</f>
-        <v/>
-      </c>
-      <c r="J58" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K58" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L58" s="18" t="n"/>
-      <c r="M58" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N58" s="17" t="inlineStr">
+      <c r="I67" s="29">
+        <f>IF(H67="","",TODAY()-H67)</f>
+        <v/>
+      </c>
+      <c r="J67" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K67" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L67" s="28" t="n"/>
+      <c r="M67" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N67" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O58" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="16" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E59)),ISNUMBER(SEARCH("thane",E59)),ISNUMBER(SEARCH("remote",E59))),"1 Mumbai/Remote",IF(OR(E59="",E59="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
+      <c r="O67" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="27" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E68)),ISNUMBER(SEARCH("thane",E68)),ISNUMBER(SEARCH("remote",E68))),"1 Mumbai/Remote",IF(OR(E68="",E68="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
         <is>
           <t>Jobcrexa</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="D68" s="17" t="inlineStr">
         <is>
           <t>Senior Java Backend Engineer (Cloud &amp; Distributed Systems)</t>
         </is>
       </c>
-      <c r="E59" s="17" t="inlineStr">
+      <c r="E68" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F59" s="16" t="inlineStr">
+      <c r="F68" s="27" t="inlineStr">
         <is>
           <t>5+ yrs</t>
         </is>
       </c>
-      <c r="G59" s="16" t="inlineStr">
+      <c r="G68" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H59" s="18" t="n">
+      <c r="H68" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I59" s="19">
-        <f>IF(H59="","",TODAY()-H59)</f>
-        <v/>
-      </c>
-      <c r="J59" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K59" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L59" s="18" t="n"/>
-      <c r="M59" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N59" s="17" t="inlineStr">
+      <c r="I68" s="29">
+        <f>IF(H68="","",TODAY()-H68)</f>
+        <v/>
+      </c>
+      <c r="J68" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K68" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L68" s="28" t="n"/>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N68" s="17" t="inlineStr">
         <is>
           <t>Java 17/21, Spring Boot 3. Confirm location</t>
         </is>
       </c>
-      <c r="O59" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="16" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E60)),ISNUMBER(SEARCH("thane",E60)),ISNUMBER(SEARCH("remote",E60))),"1 Mumbai/Remote",IF(OR(E60="",E60="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C60" s="17" t="inlineStr">
+      <c r="O68" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="27" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E69)),ISNUMBER(SEARCH("thane",E69)),ISNUMBER(SEARCH("remote",E69))),"1 Mumbai/Remote",IF(OR(E69="",E69="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D60" s="17" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
         <is>
           <t>Senior Software Engineer – Java &amp; API Integrations - Jobs</t>
         </is>
       </c>
-      <c r="E60" s="17" t="inlineStr">
+      <c r="E69" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F60" s="16" t="inlineStr">
+      <c r="F69" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G60" s="16" t="inlineStr">
+      <c r="G69" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H60" s="18" t="n">
+      <c r="H69" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I60" s="19">
-        <f>IF(H60="","",TODAY()-H60)</f>
-        <v/>
-      </c>
-      <c r="J60" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K60" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L60" s="18" t="n"/>
-      <c r="M60" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N60" s="17" t="inlineStr">
+      <c r="I69" s="29">
+        <f>IF(H69="","",TODAY()-H69)</f>
+        <v/>
+      </c>
+      <c r="J69" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K69" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L69" s="28" t="n"/>
+      <c r="M69" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N69" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O60" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E61)),ISNUMBER(SEARCH("thane",E61)),ISNUMBER(SEARCH("remote",E61))),"1 Mumbai/Remote",IF(OR(E61="",E61="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C61" s="17" t="inlineStr">
+      <c r="O69" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="27" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E70)),ISNUMBER(SEARCH("thane",E70)),ISNUMBER(SEARCH("remote",E70))),"1 Mumbai/Remote",IF(OR(E70="",E70="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
         <is>
           <t>Lacento Technologies Private Limited</t>
         </is>
       </c>
-      <c r="D61" s="17" t="inlineStr">
+      <c r="D70" s="17" t="inlineStr">
         <is>
           <t>Java Developer</t>
         </is>
       </c>
-      <c r="E61" s="17" t="inlineStr">
+      <c r="E70" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F61" s="16" t="inlineStr">
+      <c r="F70" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G61" s="16" t="inlineStr">
+      <c r="G70" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H61" s="18" t="n">
+      <c r="H70" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I61" s="19">
-        <f>IF(H61="","",TODAY()-H61)</f>
-        <v/>
-      </c>
-      <c r="J61" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K61" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L61" s="18" t="n"/>
-      <c r="M61" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N61" s="17" t="inlineStr">
+      <c r="I70" s="29">
+        <f>IF(H70="","",TODAY()-H70)</f>
+        <v/>
+      </c>
+      <c r="J70" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K70" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L70" s="28" t="n"/>
+      <c r="M70" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N70" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O61" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="16" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E62)),ISNUMBER(SEARCH("thane",E62)),ISNUMBER(SEARCH("remote",E62))),"1 Mumbai/Remote",IF(OR(E62="",E62="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C62" s="17" t="inlineStr">
+      <c r="O70" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="27" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E71)),ISNUMBER(SEARCH("thane",E71)),ISNUMBER(SEARCH("remote",E71))),"1 Mumbai/Remote",IF(OR(E71="",E71="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C71" s="17" t="inlineStr">
         <is>
           <t>VRINDA INTERNATIONAL</t>
         </is>
       </c>
-      <c r="D62" s="17" t="inlineStr">
+      <c r="D71" s="17" t="inlineStr">
         <is>
           <t>JAVA DEVELOPER</t>
         </is>
       </c>
-      <c r="E62" s="17" t="inlineStr">
+      <c r="E71" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F62" s="16" t="inlineStr">
+      <c r="F71" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G62" s="16" t="inlineStr">
+      <c r="G71" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H62" s="18" t="n">
+      <c r="H71" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I62" s="19">
-        <f>IF(H62="","",TODAY()-H62)</f>
-        <v/>
-      </c>
-      <c r="J62" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K62" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L62" s="18" t="n"/>
-      <c r="M62" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N62" s="17" t="inlineStr">
+      <c r="I71" s="29">
+        <f>IF(H71="","",TODAY()-H71)</f>
+        <v/>
+      </c>
+      <c r="J71" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K71" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L71" s="28" t="n"/>
+      <c r="M71" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N71" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O62" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="16" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E63)),ISNUMBER(SEARCH("thane",E63)),ISNUMBER(SEARCH("remote",E63))),"1 Mumbai/Remote",IF(OR(E63="",E63="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C63" s="17" t="inlineStr">
+      <c r="O71" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="27" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E72)),ISNUMBER(SEARCH("thane",E72)),ISNUMBER(SEARCH("remote",E72))),"1 Mumbai/Remote",IF(OR(E72="",E72="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C72" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D63" s="17" t="inlineStr">
+      <c r="D72" s="17" t="inlineStr">
         <is>
           <t>Backend Developer Career Guide: Stacks, Interviews, and Jobs in India</t>
         </is>
       </c>
-      <c r="E63" s="17" t="inlineStr">
+      <c r="E72" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F63" s="16" t="inlineStr">
+      <c r="F72" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G63" s="16" t="inlineStr">
+      <c r="G72" s="27" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="H63" s="18" t="n">
+      <c r="H72" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I63" s="19">
-        <f>IF(H63="","",TODAY()-H63)</f>
-        <v/>
-      </c>
-      <c r="J63" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K63" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L63" s="18" t="n"/>
-      <c r="M63" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N63" s="17" t="inlineStr">
+      <c r="I72" s="29">
+        <f>IF(H72="","",TODAY()-H72)</f>
+        <v/>
+      </c>
+      <c r="J72" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K72" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L72" s="28" t="n"/>
+      <c r="M72" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N72" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O63" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="16" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E64)),ISNUMBER(SEARCH("thane",E64)),ISNUMBER(SEARCH("remote",E64))),"1 Mumbai/Remote",IF(OR(E64="",E64="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
+      <c r="O72" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="27" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E73)),ISNUMBER(SEARCH("thane",E73)),ISNUMBER(SEARCH("remote",E73))),"1 Mumbai/Remote",IF(OR(E73="",E73="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C73" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D64" s="17" t="inlineStr">
+      <c r="D73" s="17" t="inlineStr">
         <is>
           <t>Java AWS Kafka Developer - Capgemini</t>
         </is>
       </c>
-      <c r="E64" s="17" t="inlineStr">
+      <c r="E73" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F64" s="16" t="inlineStr">
+      <c r="F73" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G64" s="16" t="inlineStr">
+      <c r="G73" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H64" s="18" t="n">
+      <c r="H73" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I64" s="19">
-        <f>IF(H64="","",TODAY()-H64)</f>
-        <v/>
-      </c>
-      <c r="J64" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K64" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L64" s="18" t="n"/>
-      <c r="M64" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N64" s="17" t="inlineStr">
+      <c r="I73" s="29">
+        <f>IF(H73="","",TODAY()-H73)</f>
+        <v/>
+      </c>
+      <c r="J73" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K73" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L73" s="28" t="n"/>
+      <c r="M73" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N73" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O64" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="16" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E65)),ISNUMBER(SEARCH("thane",E65)),ISNUMBER(SEARCH("remote",E65))),"1 Mumbai/Remote",IF(OR(E65="",E65="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C65" s="17" t="inlineStr">
+      <c r="O73" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="27" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E74)),ISNUMBER(SEARCH("thane",E74)),ISNUMBER(SEARCH("remote",E74))),"1 Mumbai/Remote",IF(OR(E74="",E74="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D65" s="17" t="inlineStr">
+      <c r="D74" s="17" t="inlineStr">
         <is>
           <t>We are looking for experienced Frontend / Full Stack Developers ...</t>
         </is>
       </c>
-      <c r="E65" s="17" t="inlineStr">
+      <c r="E74" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F65" s="16" t="inlineStr">
+      <c r="F74" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G65" s="16" t="inlineStr">
+      <c r="G74" s="27" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="H65" s="18" t="n">
+      <c r="H74" s="28" t="n">
         <v>46302</v>
       </c>
-      <c r="I65" s="19">
-        <f>IF(H65="","",TODAY()-H65)</f>
-        <v/>
-      </c>
-      <c r="J65" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K65" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L65" s="18" t="n"/>
-      <c r="M65" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N65" s="17" t="inlineStr">
+      <c r="I74" s="29">
+        <f>IF(H74="","",TODAY()-H74)</f>
+        <v/>
+      </c>
+      <c r="J74" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K74" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L74" s="28" t="n"/>
+      <c r="M74" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N74" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O65" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E66)),ISNUMBER(SEARCH("thane",E66)),ISNUMBER(SEARCH("remote",E66))),"1 Mumbai/Remote",IF(OR(E66="",E66="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C66" s="17" t="inlineStr">
+      <c r="O74" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="27" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E75)),ISNUMBER(SEARCH("thane",E75)),ISNUMBER(SEARCH("remote",E75))),"1 Mumbai/Remote",IF(OR(E75="",E75="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C75" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="D75" s="17" t="inlineStr">
         <is>
           <t>Lead Backend Engineer - Java Spring Boot</t>
         </is>
       </c>
-      <c r="E66" s="17" t="inlineStr">
+      <c r="E75" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F66" s="16" t="inlineStr">
+      <c r="F75" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G66" s="16" t="inlineStr">
+      <c r="G75" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H66" s="18" t="n">
+      <c r="H75" s="28" t="n">
         <v>46302</v>
       </c>
-      <c r="I66" s="19">
-        <f>IF(H66="","",TODAY()-H66)</f>
-        <v/>
-      </c>
-      <c r="J66" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K66" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L66" s="18" t="n"/>
-      <c r="M66" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N66" s="17" t="inlineStr">
+      <c r="I75" s="29">
+        <f>IF(H75="","",TODAY()-H75)</f>
+        <v/>
+      </c>
+      <c r="J75" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K75" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L75" s="28" t="n"/>
+      <c r="M75" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N75" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O66" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="16" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E67)),ISNUMBER(SEARCH("thane",E67)),ISNUMBER(SEARCH("remote",E67))),"1 Mumbai/Remote",IF(OR(E67="",E67="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C67" s="17" t="inlineStr">
+      <c r="O75" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="27" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E76)),ISNUMBER(SEARCH("thane",E76)),ISNUMBER(SEARCH("remote",E76))),"1 Mumbai/Remote",IF(OR(E76="",E76="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D67" s="17" t="inlineStr">
+      <c r="D76" s="17" t="inlineStr">
         <is>
           <t>Sr. Java Spring boot Developer - Concentrix</t>
         </is>
       </c>
-      <c r="E67" s="17" t="inlineStr">
+      <c r="E76" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F67" s="16" t="inlineStr">
+      <c r="F76" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G67" s="16" t="inlineStr">
+      <c r="G76" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H67" s="18" t="n">
+      <c r="H76" s="28" t="n">
         <v>46302</v>
       </c>
-      <c r="I67" s="19">
-        <f>IF(H67="","",TODAY()-H67)</f>
-        <v/>
-      </c>
-      <c r="J67" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K67" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L67" s="18" t="n"/>
-      <c r="M67" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N67" s="17" t="inlineStr">
+      <c r="I76" s="29">
+        <f>IF(H76="","",TODAY()-H76)</f>
+        <v/>
+      </c>
+      <c r="J76" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K76" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L76" s="28" t="n"/>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N76" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O67" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="16" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E68)),ISNUMBER(SEARCH("thane",E68)),ISNUMBER(SEARCH("remote",E68))),"1 Mumbai/Remote",IF(OR(E68="",E68="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C68" s="17" t="inlineStr">
+      <c r="O76" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="27" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E77)),ISNUMBER(SEARCH("thane",E77)),ISNUMBER(SEARCH("remote",E77))),"1 Mumbai/Remote",IF(OR(E77="",E77="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C77" s="17" t="inlineStr">
         <is>
           <t>Scholastika Knowledge Base</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="D77" s="17" t="inlineStr">
         <is>
           <t>Senior Java Software Engineer</t>
         </is>
       </c>
-      <c r="E68" s="17" t="inlineStr">
+      <c r="E77" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F68" s="16" t="inlineStr">
+      <c r="F77" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G68" s="16" t="inlineStr">
+      <c r="G77" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H68" s="18" t="n">
+      <c r="H77" s="28" t="n">
         <v>46308</v>
       </c>
-      <c r="I68" s="19">
-        <f>IF(H68="","",TODAY()-H68)</f>
-        <v/>
-      </c>
-      <c r="J68" s="16" t="inlineStr">
+      <c r="I77" s="29">
+        <f>IF(H77="","",TODAY()-H77)</f>
+        <v/>
+      </c>
+      <c r="J77" s="27" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K68" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L68" s="18" t="n"/>
-      <c r="M68" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N68" s="17" t="inlineStr">
+      <c r="K77" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L77" s="28" t="n"/>
+      <c r="M77" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N77" s="17" t="inlineStr">
         <is>
           <t>Small company; confirm location</t>
         </is>
       </c>
-      <c r="O68" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="16" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E69)),ISNUMBER(SEARCH("thane",E69)),ISNUMBER(SEARCH("remote",E69))),"1 Mumbai/Remote",IF(OR(E69="",E69="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C69" s="17" t="inlineStr">
+      <c r="O77" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="27" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E78)),ISNUMBER(SEARCH("thane",E78)),ISNUMBER(SEARCH("remote",E78))),"1 Mumbai/Remote",IF(OR(E78="",E78="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
         <is>
           <t>GiantMind Solutions</t>
         </is>
       </c>
-      <c r="D69" s="17" t="inlineStr">
+      <c r="D78" s="17" t="inlineStr">
         <is>
           <t>Sr Java Developer</t>
         </is>
       </c>
-      <c r="E69" s="17" t="inlineStr">
+      <c r="E78" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F69" s="16" t="inlineStr">
+      <c r="F78" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G69" s="16" t="inlineStr">
+      <c r="G78" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H69" s="18" t="n">
+      <c r="H78" s="28" t="n">
         <v>46308</v>
       </c>
-      <c r="I69" s="19">
-        <f>IF(H69="","",TODAY()-H69)</f>
-        <v/>
-      </c>
-      <c r="J69" s="16" t="inlineStr">
+      <c r="I78" s="29">
+        <f>IF(H78="","",TODAY()-H78)</f>
+        <v/>
+      </c>
+      <c r="J78" s="27" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K69" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L69" s="18" t="n"/>
-      <c r="M69" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N69" s="17" t="inlineStr">
+      <c r="K78" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L78" s="28" t="n"/>
+      <c r="M78" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N78" s="17" t="inlineStr">
         <is>
           <t>Listed as India; confirm location</t>
         </is>
       </c>
-      <c r="O69" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="16" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E70)),ISNUMBER(SEARCH("thane",E70)),ISNUMBER(SEARCH("remote",E70))),"1 Mumbai/Remote",IF(OR(E70="",E70="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C70" s="17" t="inlineStr">
+      <c r="O78" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="27" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E79)),ISNUMBER(SEARCH("thane",E79)),ISNUMBER(SEARCH("remote",E79))),"1 Mumbai/Remote",IF(OR(E79="",E79="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C79" s="17" t="inlineStr">
         <is>
           <t>InfoBeans</t>
         </is>
       </c>
-      <c r="D70" s="17" t="inlineStr">
+      <c r="D79" s="17" t="inlineStr">
         <is>
           <t>Senior Java Software Engineer</t>
         </is>
       </c>
-      <c r="E70" s="17" t="inlineStr">
+      <c r="E79" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F70" s="16" t="inlineStr">
+      <c r="F79" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G70" s="16" t="inlineStr">
+      <c r="G79" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H70" s="18" t="n">
+      <c r="H79" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="I70" s="19">
-        <f>IF(H70="","",TODAY()-H70)</f>
-        <v/>
-      </c>
-      <c r="J70" s="16" t="inlineStr">
+      <c r="I79" s="29">
+        <f>IF(H79="","",TODAY()-H79)</f>
+        <v/>
+      </c>
+      <c r="J79" s="27" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K70" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L70" s="18" t="n"/>
-      <c r="M70" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N70" s="17" t="inlineStr">
+      <c r="K79" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L79" s="28" t="n"/>
+      <c r="M79" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N79" s="17" t="inlineStr">
         <is>
           <t>Confirm location</t>
         </is>
       </c>
-      <c r="O70" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="16" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E71)),ISNUMBER(SEARCH("thane",E71)),ISNUMBER(SEARCH("remote",E71))),"1 Mumbai/Remote",IF(OR(E71="",E71="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C71" s="17" t="inlineStr">
+      <c r="O79" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="27" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E80)),ISNUMBER(SEARCH("thane",E80)),ISNUMBER(SEARCH("remote",E80))),"1 Mumbai/Remote",IF(OR(E80="",E80="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
         <is>
           <t>Cloudesign</t>
         </is>
       </c>
-      <c r="D71" s="17" t="inlineStr">
+      <c r="D80" s="17" t="inlineStr">
         <is>
           <t>Senior Java Developer</t>
         </is>
       </c>
-      <c r="E71" s="17" t="inlineStr">
+      <c r="E80" s="17" t="inlineStr">
         <is>
           <t>Verify</t>
         </is>
       </c>
-      <c r="F71" s="16" t="inlineStr">
+      <c r="F80" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G71" s="16" t="inlineStr">
+      <c r="G80" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H71" s="18" t="n">
+      <c r="H80" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I71" s="19">
-        <f>IF(H71="","",TODAY()-H71)</f>
-        <v/>
-      </c>
-      <c r="J71" s="16" t="inlineStr">
+      <c r="I80" s="29">
+        <f>IF(H80="","",TODAY()-H80)</f>
+        <v/>
+      </c>
+      <c r="J80" s="27" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K71" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L71" s="18" t="n"/>
-      <c r="M71" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N71" s="17" t="inlineStr">
+      <c r="K80" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L80" s="28" t="n"/>
+      <c r="M80" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N80" s="17" t="inlineStr">
         <is>
           <t>Confirm location</t>
         </is>
       </c>
-      <c r="O71" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="16" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E72)),ISNUMBER(SEARCH("thane",E72)),ISNUMBER(SEARCH("remote",E72))),"1 Mumbai/Remote",IF(OR(E72="",E72="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C72" s="17" t="inlineStr">
+      <c r="O80" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E81)),ISNUMBER(SEARCH("thane",E81)),ISNUMBER(SEARCH("remote",E81))),"1 Mumbai/Remote",IF(OR(E81="",E81="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C81" s="17" t="inlineStr">
         <is>
           <t>Questhiring</t>
         </is>
       </c>
-      <c r="D72" s="17" t="inlineStr">
+      <c r="D81" s="17" t="inlineStr">
         <is>
           <t>Java Software Engineer</t>
         </is>
       </c>
-      <c r="E72" s="17" t="inlineStr">
+      <c r="E81" s="17" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F72" s="16" t="inlineStr">
+      <c r="F81" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G72" s="16" t="inlineStr">
+      <c r="G81" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H72" s="18" t="n">
+      <c r="H81" s="28" t="n">
         <v>46308</v>
       </c>
-      <c r="I72" s="19">
-        <f>IF(H72="","",TODAY()-H72)</f>
-        <v/>
-      </c>
-      <c r="J72" s="16" t="inlineStr">
+      <c r="I81" s="29">
+        <f>IF(H81="","",TODAY()-H81)</f>
+        <v/>
+      </c>
+      <c r="J81" s="27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K72" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L72" s="18" t="n"/>
-      <c r="M72" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N72" s="17" t="inlineStr">
+      <c r="K81" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L81" s="28" t="n"/>
+      <c r="M81" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N81" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O72" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="16" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E73)),ISNUMBER(SEARCH("thane",E73)),ISNUMBER(SEARCH("remote",E73))),"1 Mumbai/Remote",IF(OR(E73="",E73="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C73" s="17" t="inlineStr">
+      <c r="O81" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="27" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E82)),ISNUMBER(SEARCH("thane",E82)),ISNUMBER(SEARCH("remote",E82))),"1 Mumbai/Remote",IF(OR(E82="",E82="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C82" s="17" t="inlineStr">
         <is>
           <t>NTT DATA</t>
         </is>
       </c>
-      <c r="D73" s="17" t="inlineStr">
+      <c r="D82" s="17" t="inlineStr">
         <is>
           <t>Software Engineer - Java, Spring Boot, Kafka</t>
         </is>
       </c>
-      <c r="E73" s="17" t="inlineStr">
+      <c r="E82" s="17" t="inlineStr">
         <is>
           <t>Hyderabad / Chennai / Bengaluru</t>
         </is>
       </c>
-      <c r="F73" s="16" t="inlineStr">
+      <c r="F82" s="27" t="inlineStr">
         <is>
           <t>5-7 yrs</t>
         </is>
       </c>
-      <c r="G73" s="16" t="inlineStr">
+      <c r="G82" s="27" t="inlineStr">
         <is>
           <t>Naukri</t>
         </is>
       </c>
-      <c r="H73" s="18" t="n">
+      <c r="H82" s="28" t="n">
         <v>46305</v>
       </c>
-      <c r="I73" s="19">
-        <f>IF(H73="","",TODAY()-H73)</f>
-        <v/>
-      </c>
-      <c r="J73" s="16" t="inlineStr">
+      <c r="I82" s="29">
+        <f>IF(H82="","",TODAY()-H82)</f>
+        <v/>
+      </c>
+      <c r="J82" s="27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K73" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L73" s="18" t="n"/>
-      <c r="M73" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N73" s="17" t="inlineStr">
+      <c r="K82" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L82" s="28" t="n"/>
+      <c r="M82" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N82" s="17" t="inlineStr">
         <is>
           <t>Good experience match</t>
         </is>
       </c>
-      <c r="O73" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="16" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E74)),ISNUMBER(SEARCH("thane",E74)),ISNUMBER(SEARCH("remote",E74))),"1 Mumbai/Remote",IF(OR(E74="",E74="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C74" s="17" t="inlineStr">
+      <c r="O82" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="27" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E83)),ISNUMBER(SEARCH("thane",E83)),ISNUMBER(SEARCH("remote",E83))),"1 Mumbai/Remote",IF(OR(E83="",E83="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C83" s="17" t="inlineStr">
         <is>
           <t>Q3 Technologies</t>
         </is>
       </c>
-      <c r="D74" s="17" t="inlineStr">
+      <c r="D83" s="17" t="inlineStr">
         <is>
           <t>Senior Java Developer (Java 17, Spring Boot)</t>
         </is>
       </c>
-      <c r="E74" s="17" t="inlineStr">
+      <c r="E83" s="17" t="inlineStr">
         <is>
           <t>Bengaluru / Gurugram</t>
         </is>
       </c>
-      <c r="F74" s="16" t="inlineStr">
+      <c r="F83" s="27" t="inlineStr">
         <is>
           <t>5-6 yrs</t>
         </is>
       </c>
-      <c r="G74" s="16" t="inlineStr">
+      <c r="G83" s="27" t="inlineStr">
         <is>
           <t>Naukri</t>
         </is>
       </c>
-      <c r="H74" s="18" t="n">
+      <c r="H83" s="28" t="n">
         <v>46305</v>
       </c>
-      <c r="I74" s="19">
-        <f>IF(H74="","",TODAY()-H74)</f>
-        <v/>
-      </c>
-      <c r="J74" s="16" t="inlineStr">
+      <c r="I83" s="29">
+        <f>IF(H83="","",TODAY()-H83)</f>
+        <v/>
+      </c>
+      <c r="J83" s="27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K74" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L74" s="18" t="n"/>
-      <c r="M74" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N74" s="17" t="inlineStr">
+      <c r="K83" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L83" s="28" t="n"/>
+      <c r="M83" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N83" s="17" t="inlineStr">
         <is>
           <t>Exact experience band</t>
         </is>
       </c>
-      <c r="O74" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="16" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E75)),ISNUMBER(SEARCH("thane",E75)),ISNUMBER(SEARCH("remote",E75))),"1 Mumbai/Remote",IF(OR(E75="",E75="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C75" s="17" t="inlineStr">
+      <c r="O83" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="27" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E84)),ISNUMBER(SEARCH("thane",E84)),ISNUMBER(SEARCH("remote",E84))),"1 Mumbai/Remote",IF(OR(E84="",E84="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
         <is>
           <t>Virtusa</t>
         </is>
       </c>
-      <c r="D75" s="17" t="inlineStr">
+      <c r="D84" s="17" t="inlineStr">
         <is>
           <t>Java Backend</t>
         </is>
       </c>
-      <c r="E75" s="17" t="inlineStr">
+      <c r="E84" s="17" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F75" s="16" t="inlineStr">
+      <c r="F84" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G75" s="16" t="inlineStr">
+      <c r="G84" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H75" s="18" t="n">
+      <c r="H84" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I75" s="19">
-        <f>IF(H75="","",TODAY()-H75)</f>
-        <v/>
-      </c>
-      <c r="J75" s="16" t="inlineStr">
+      <c r="I84" s="29">
+        <f>IF(H84="","",TODAY()-H84)</f>
+        <v/>
+      </c>
+      <c r="J84" s="27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K75" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L75" s="18" t="n"/>
-      <c r="M75" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N75" s="17" t="inlineStr">
+      <c r="K84" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L84" s="28" t="n"/>
+      <c r="M84" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N84" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O75" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="16" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E76)),ISNUMBER(SEARCH("thane",E76)),ISNUMBER(SEARCH("remote",E76))),"1 Mumbai/Remote",IF(OR(E76="",E76="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C76" s="17" t="inlineStr">
+      <c r="O84" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="27" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E85)),ISNUMBER(SEARCH("thane",E85)),ISNUMBER(SEARCH("remote",E85))),"1 Mumbai/Remote",IF(OR(E85="",E85="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
         <is>
           <t>TestUnity</t>
         </is>
       </c>
-      <c r="D76" s="17" t="inlineStr">
+      <c r="D85" s="17" t="inlineStr">
         <is>
           <t>Team Leader – Java Spring Boot | Telecom</t>
         </is>
       </c>
-      <c r="E76" s="17" t="inlineStr">
+      <c r="E85" s="17" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F76" s="16" t="inlineStr">
+      <c r="F85" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G76" s="16" t="inlineStr">
+      <c r="G85" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H76" s="18" t="n">
+      <c r="H85" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I76" s="19">
-        <f>IF(H76="","",TODAY()-H76)</f>
-        <v/>
-      </c>
-      <c r="J76" s="16" t="inlineStr">
+      <c r="I85" s="29">
+        <f>IF(H85="","",TODAY()-H85)</f>
+        <v/>
+      </c>
+      <c r="J85" s="27" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K76" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L76" s="18" t="n"/>
-      <c r="M76" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N76" s="17" t="inlineStr">
+      <c r="K85" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L85" s="28" t="n"/>
+      <c r="M85" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N85" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O76" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="16" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E77)),ISNUMBER(SEARCH("thane",E77)),ISNUMBER(SEARCH("remote",E77))),"1 Mumbai/Remote",IF(OR(E77="",E77="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C77" s="17" t="inlineStr">
+      <c r="O85" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="27" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E86)),ISNUMBER(SEARCH("thane",E86)),ISNUMBER(SEARCH("remote",E86))),"1 Mumbai/Remote",IF(OR(E86="",E86="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C86" s="17" t="inlineStr">
         <is>
           <t>Bengaluru - Amtech</t>
         </is>
       </c>
-      <c r="D77" s="17" t="inlineStr">
+      <c r="D86" s="17" t="inlineStr">
         <is>
           <t>Java Developer</t>
         </is>
       </c>
-      <c r="E77" s="17" t="inlineStr">
+      <c r="E86" s="17" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F77" s="16" t="inlineStr">
+      <c r="F86" s="27" t="inlineStr">
         <is>
           <t>4-9 yrs</t>
         </is>
       </c>
-      <c r="G77" s="16" t="inlineStr">
+      <c r="G86" s="27" t="inlineStr">
         <is>
           <t>Naukri</t>
         </is>
       </c>
-      <c r="H77" s="18" t="n">
+      <c r="H86" s="28" t="n">
         <v>46306</v>
       </c>
-      <c r="I77" s="19">
-        <f>IF(H77="","",TODAY()-H77)</f>
-        <v/>
-      </c>
-      <c r="J77" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K77" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L77" s="18" t="n"/>
-      <c r="M77" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N77" s="17" t="inlineStr">
+      <c r="I86" s="29">
+        <f>IF(H86="","",TODAY()-H86)</f>
+        <v/>
+      </c>
+      <c r="J86" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K86" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L86" s="28" t="n"/>
+      <c r="M86" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N86" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O77" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="16" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E78)),ISNUMBER(SEARCH("thane",E78)),ISNUMBER(SEARCH("remote",E78))),"1 Mumbai/Remote",IF(OR(E78="",E78="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C78" s="17" t="inlineStr">
+      <c r="O86" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E87)),ISNUMBER(SEARCH("thane",E87)),ISNUMBER(SEARCH("remote",E87))),"1 Mumbai/Remote",IF(OR(E87="",E87="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C87" s="17" t="inlineStr">
         <is>
           <t>Bengaluru - Coxvi Technologies</t>
         </is>
       </c>
-      <c r="D78" s="17" t="inlineStr">
+      <c r="D87" s="17" t="inlineStr">
         <is>
           <t>Back End Engineer</t>
         </is>
       </c>
-      <c r="E78" s="17" t="inlineStr">
+      <c r="E87" s="17" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F78" s="16" t="inlineStr">
+      <c r="F87" s="27" t="inlineStr">
         <is>
           <t>5-8 yrs</t>
         </is>
       </c>
-      <c r="G78" s="16" t="inlineStr">
+      <c r="G87" s="27" t="inlineStr">
         <is>
           <t>Naukri</t>
         </is>
       </c>
-      <c r="H78" s="18" t="n">
+      <c r="H87" s="28" t="n">
         <v>46306</v>
       </c>
-      <c r="I78" s="19">
-        <f>IF(H78="","",TODAY()-H78)</f>
-        <v/>
-      </c>
-      <c r="J78" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K78" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L78" s="18" t="n"/>
-      <c r="M78" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N78" s="17" t="inlineStr">
+      <c r="I87" s="29">
+        <f>IF(H87="","",TODAY()-H87)</f>
+        <v/>
+      </c>
+      <c r="J87" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K87" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L87" s="28" t="n"/>
+      <c r="M87" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N87" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O78" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="16" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E79)),ISNUMBER(SEARCH("thane",E79)),ISNUMBER(SEARCH("remote",E79))),"1 Mumbai/Remote",IF(OR(E79="",E79="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C79" s="17" t="inlineStr">
+      <c r="O87" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="27" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E88)),ISNUMBER(SEARCH("thane",E88)),ISNUMBER(SEARCH("remote",E88))),"1 Mumbai/Remote",IF(OR(E88="",E88="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
         <is>
           <t>AgileEngine</t>
         </is>
       </c>
-      <c r="D79" s="17" t="inlineStr">
+      <c r="D88" s="17" t="inlineStr">
         <is>
           <t>Senior Java Engineer ID93313</t>
         </is>
       </c>
-      <c r="E79" s="17" t="inlineStr">
+      <c r="E88" s="17" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F79" s="16" t="inlineStr">
+      <c r="F88" s="27" t="inlineStr">
         <is>
           <t>4+ yrs</t>
         </is>
       </c>
-      <c r="G79" s="16" t="inlineStr">
+      <c r="G88" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H79" s="18" t="n">
+      <c r="H88" s="28" t="n">
         <v>46306</v>
       </c>
-      <c r="I79" s="19">
-        <f>IF(H79="","",TODAY()-H79)</f>
-        <v/>
-      </c>
-      <c r="J79" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K79" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L79" s="18" t="n"/>
-      <c r="M79" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N79" s="17" t="inlineStr">
+      <c r="I88" s="29">
+        <f>IF(H88="","",TODAY()-H88)</f>
+        <v/>
+      </c>
+      <c r="J88" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K88" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L88" s="28" t="n"/>
+      <c r="M88" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N88" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O79" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="16" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E80)),ISNUMBER(SEARCH("thane",E80)),ISNUMBER(SEARCH("remote",E80))),"1 Mumbai/Remote",IF(OR(E80="",E80="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C80" s="17" t="inlineStr">
+      <c r="O88" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="27" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E89)),ISNUMBER(SEARCH("thane",E89)),ISNUMBER(SEARCH("remote",E89))),"1 Mumbai/Remote",IF(OR(E89="",E89="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C89" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D80" s="17" t="inlineStr">
+      <c r="D89" s="17" t="inlineStr">
         <is>
           <t>Java Fullstack(Angular/React) with Python+AI - 5 to 8 years of experience</t>
         </is>
       </c>
-      <c r="E80" s="17" t="inlineStr">
+      <c r="E89" s="17" t="inlineStr">
         <is>
           <t>Bengaluru / Chennai / Noida</t>
         </is>
       </c>
-      <c r="F80" s="16" t="inlineStr">
+      <c r="F89" s="27" t="inlineStr">
         <is>
           <t>5-8 yrs</t>
         </is>
       </c>
-      <c r="G80" s="16" t="inlineStr">
+      <c r="G89" s="27" t="inlineStr">
         <is>
           <t>Naukri</t>
         </is>
       </c>
-      <c r="H80" s="18" t="n">
+      <c r="H89" s="28" t="n">
         <v>46306</v>
       </c>
-      <c r="I80" s="19">
-        <f>IF(H80="","",TODAY()-H80)</f>
-        <v/>
-      </c>
-      <c r="J80" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K80" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L80" s="18" t="n"/>
-      <c r="M80" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N80" s="17" t="inlineStr">
+      <c r="I89" s="29">
+        <f>IF(H89="","",TODAY()-H89)</f>
+        <v/>
+      </c>
+      <c r="J89" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K89" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L89" s="28" t="n"/>
+      <c r="M89" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N89" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O80" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="16" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E81)),ISNUMBER(SEARCH("thane",E81)),ISNUMBER(SEARCH("remote",E81))),"1 Mumbai/Remote",IF(OR(E81="",E81="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C81" s="17" t="inlineStr">
+      <c r="O89" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="27" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E90)),ISNUMBER(SEARCH("thane",E90)),ISNUMBER(SEARCH("remote",E90))),"1 Mumbai/Remote",IF(OR(E90="",E90="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C90" s="17" t="inlineStr">
         <is>
           <t>Innova Solutions</t>
         </is>
       </c>
-      <c r="D81" s="17" t="inlineStr">
+      <c r="D90" s="17" t="inlineStr">
         <is>
           <t>Java Developer (Kafka, Spring Boot)</t>
         </is>
       </c>
-      <c r="E81" s="17" t="inlineStr">
+      <c r="E90" s="17" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F81" s="16" t="inlineStr">
+      <c r="F90" s="27" t="inlineStr">
         <is>
           <t>6-10 yrs</t>
         </is>
       </c>
-      <c r="G81" s="16" t="inlineStr">
+      <c r="G90" s="27" t="inlineStr">
         <is>
           <t>Naukri</t>
         </is>
       </c>
-      <c r="H81" s="18" t="n">
+      <c r="H90" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I81" s="19">
-        <f>IF(H81="","",TODAY()-H81)</f>
-        <v/>
-      </c>
-      <c r="J81" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K81" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L81" s="18" t="n"/>
-      <c r="M81" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N81" s="17" t="inlineStr">
+      <c r="I90" s="29">
+        <f>IF(H90="","",TODAY()-H90)</f>
+        <v/>
+      </c>
+      <c r="J90" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K90" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L90" s="28" t="n"/>
+      <c r="M90" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N90" s="17" t="inlineStr">
         <is>
           <t>Stretch on experience</t>
         </is>
       </c>
-      <c r="O81" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="16" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E82)),ISNUMBER(SEARCH("thane",E82)),ISNUMBER(SEARCH("remote",E82))),"1 Mumbai/Remote",IF(OR(E82="",E82="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C82" s="17" t="inlineStr">
+      <c r="O90" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="27" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E91)),ISNUMBER(SEARCH("thane",E91)),ISNUMBER(SEARCH("remote",E91))),"1 Mumbai/Remote",IF(OR(E91="",E91="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C91" s="17" t="inlineStr">
         <is>
           <t>Ahmedabad - Brilworks</t>
         </is>
       </c>
-      <c r="D82" s="17" t="inlineStr">
+      <c r="D91" s="17" t="inlineStr">
         <is>
           <t>Senior Java Developer</t>
         </is>
       </c>
-      <c r="E82" s="17" t="inlineStr">
+      <c r="E91" s="17" t="inlineStr">
         <is>
           <t>Ahmedabad</t>
         </is>
       </c>
-      <c r="F82" s="16" t="inlineStr">
+      <c r="F91" s="27" t="inlineStr">
         <is>
           <t>3-5 yrs</t>
         </is>
       </c>
-      <c r="G82" s="16" t="inlineStr">
+      <c r="G91" s="27" t="inlineStr">
         <is>
           <t>Naukri</t>
         </is>
       </c>
-      <c r="H82" s="18" t="n">
+      <c r="H91" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I82" s="19">
-        <f>IF(H82="","",TODAY()-H82)</f>
-        <v/>
-      </c>
-      <c r="J82" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K82" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L82" s="18" t="n"/>
-      <c r="M82" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N82" s="17" t="inlineStr">
+      <c r="I91" s="29">
+        <f>IF(H91="","",TODAY()-H91)</f>
+        <v/>
+      </c>
+      <c r="J91" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K91" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L91" s="28" t="n"/>
+      <c r="M91" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N91" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O82" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="16" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E83)),ISNUMBER(SEARCH("thane",E83)),ISNUMBER(SEARCH("remote",E83))),"1 Mumbai/Remote",IF(OR(E83="",E83="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C83" s="17" t="inlineStr">
+      <c r="O91" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="27" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E92)),ISNUMBER(SEARCH("thane",E92)),ISNUMBER(SEARCH("remote",E92))),"1 Mumbai/Remote",IF(OR(E92="",E92="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C92" s="17" t="inlineStr">
         <is>
           <t>See link</t>
         </is>
       </c>
-      <c r="D83" s="17" t="inlineStr">
+      <c r="D92" s="17" t="inlineStr">
         <is>
           <t>Java React FullStack Developer - Deloitte US-India Offices - Naukri.com</t>
         </is>
       </c>
-      <c r="E83" s="17" t="inlineStr">
+      <c r="E92" s="17" t="inlineStr">
         <is>
           <t>Bengaluru / Chennai / Hyderabad</t>
         </is>
       </c>
-      <c r="F83" s="16" t="inlineStr">
+      <c r="F92" s="27" t="inlineStr">
         <is>
           <t>3-8 yrs</t>
         </is>
       </c>
-      <c r="G83" s="16" t="inlineStr">
+      <c r="G92" s="27" t="inlineStr">
         <is>
           <t>Naukri</t>
         </is>
       </c>
-      <c r="H83" s="18" t="n">
+      <c r="H92" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I83" s="19">
-        <f>IF(H83="","",TODAY()-H83)</f>
-        <v/>
-      </c>
-      <c r="J83" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K83" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L83" s="18" t="n"/>
-      <c r="M83" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N83" s="17" t="inlineStr">
+      <c r="I92" s="29">
+        <f>IF(H92="","",TODAY()-H92)</f>
+        <v/>
+      </c>
+      <c r="J92" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K92" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L92" s="28" t="n"/>
+      <c r="M92" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N92" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O83" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="16" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E84)),ISNUMBER(SEARCH("thane",E84)),ISNUMBER(SEARCH("remote",E84))),"1 Mumbai/Remote",IF(OR(E84="",E84="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C84" s="17" t="inlineStr">
+      <c r="O92" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="27" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E93)),ISNUMBER(SEARCH("thane",E93)),ISNUMBER(SEARCH("remote",E93))),"1 Mumbai/Remote",IF(OR(E93="",E93="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C93" s="17" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="D84" s="17" t="inlineStr">
+      <c r="D93" s="17" t="inlineStr">
         <is>
           <t>Golang Developer (SDE2)</t>
         </is>
       </c>
-      <c r="E84" s="17" t="inlineStr">
+      <c r="E93" s="17" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="F84" s="16" t="inlineStr">
+      <c r="F93" s="27" t="inlineStr">
         <is>
           <t>4-6 yrs</t>
         </is>
       </c>
-      <c r="G84" s="16" t="inlineStr">
+      <c r="G93" s="27" t="inlineStr">
         <is>
           <t>Naukri</t>
         </is>
       </c>
-      <c r="H84" s="18" t="n">
+      <c r="H93" s="28" t="n">
         <v>46304</v>
       </c>
-      <c r="I84" s="19">
-        <f>IF(H84="","",TODAY()-H84)</f>
-        <v/>
-      </c>
-      <c r="J84" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K84" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L84" s="18" t="n"/>
-      <c r="M84" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N84" s="17" t="inlineStr">
+      <c r="I93" s="29">
+        <f>IF(H93="","",TODAY()-H93)</f>
+        <v/>
+      </c>
+      <c r="J93" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K93" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L93" s="28" t="n"/>
+      <c r="M93" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N93" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O84" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="16" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E85)),ISNUMBER(SEARCH("thane",E85)),ISNUMBER(SEARCH("remote",E85))),"1 Mumbai/Remote",IF(OR(E85="",E85="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C85" s="17" t="inlineStr">
+      <c r="O93" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="27" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E94)),ISNUMBER(SEARCH("thane",E94)),ISNUMBER(SEARCH("remote",E94))),"1 Mumbai/Remote",IF(OR(E94="",E94="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
         <is>
           <t>Blue Yonder</t>
         </is>
       </c>
-      <c r="D85" s="17" t="inlineStr">
+      <c r="D94" s="17" t="inlineStr">
         <is>
           <t>Lead Software Engineer - Java, Spring Boot, Microservices, Kafka, Azure</t>
         </is>
       </c>
-      <c r="E85" s="17" t="inlineStr">
+      <c r="E94" s="17" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F85" s="16" t="inlineStr">
+      <c r="F94" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G85" s="16" t="inlineStr">
+      <c r="G94" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H85" s="18" t="n">
+      <c r="H94" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I85" s="19">
-        <f>IF(H85="","",TODAY()-H85)</f>
-        <v/>
-      </c>
-      <c r="J85" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K85" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L85" s="18" t="n"/>
-      <c r="M85" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N85" s="17" t="inlineStr">
+      <c r="I94" s="29">
+        <f>IF(H94="","",TODAY()-H94)</f>
+        <v/>
+      </c>
+      <c r="J94" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K94" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L94" s="28" t="n"/>
+      <c r="M94" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N94" s="17" t="inlineStr">
         <is>
           <t>Lead level - stretch</t>
         </is>
       </c>
-      <c r="O85" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="16" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E86)),ISNUMBER(SEARCH("thane",E86)),ISNUMBER(SEARCH("remote",E86))),"1 Mumbai/Remote",IF(OR(E86="",E86="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C86" s="17" t="inlineStr">
+      <c r="O94" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="27" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E95)),ISNUMBER(SEARCH("thane",E95)),ISNUMBER(SEARCH("remote",E95))),"1 Mumbai/Remote",IF(OR(E95="",E95="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C95" s="17" t="inlineStr">
         <is>
           <t>VARITE INC</t>
         </is>
       </c>
-      <c r="D86" s="17" t="inlineStr">
+      <c r="D95" s="17" t="inlineStr">
         <is>
           <t>Java Azure Developer</t>
         </is>
       </c>
-      <c r="E86" s="17" t="inlineStr">
+      <c r="E95" s="17" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F86" s="16" t="inlineStr">
+      <c r="F95" s="27" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="G86" s="16" t="inlineStr">
+      <c r="G95" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="H86" s="18" t="n">
+      <c r="H95" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I86" s="19">
-        <f>IF(H86="","",TODAY()-H86)</f>
-        <v/>
-      </c>
-      <c r="J86" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K86" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L86" s="18" t="n"/>
-      <c r="M86" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N86" s="17" t="inlineStr">
+      <c r="I95" s="29">
+        <f>IF(H95="","",TODAY()-H95)</f>
+        <v/>
+      </c>
+      <c r="J95" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K95" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L95" s="28" t="n"/>
+      <c r="M95" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N95" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O86" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="16" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E87)),ISNUMBER(SEARCH("thane",E87)),ISNUMBER(SEARCH("remote",E87))),"1 Mumbai/Remote",IF(OR(E87="",E87="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C87" s="17" t="inlineStr">
+      <c r="O95" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="27" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E96)),ISNUMBER(SEARCH("thane",E96)),ISNUMBER(SEARCH("remote",E96))),"1 Mumbai/Remote",IF(OR(E96="",E96="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C96" s="17" t="inlineStr">
         <is>
           <t>Full Stack - Damco Solutions</t>
         </is>
       </c>
-      <c r="D87" s="17" t="inlineStr">
+      <c r="D96" s="17" t="inlineStr">
         <is>
           <t>Java Developer</t>
         </is>
       </c>
-      <c r="E87" s="17" t="inlineStr">
+      <c r="E96" s="17" t="inlineStr">
         <is>
           <t>Noida</t>
         </is>
       </c>
-      <c r="F87" s="16" t="inlineStr">
+      <c r="F96" s="27" t="inlineStr">
         <is>
           <t>4-9 yrs</t>
         </is>
       </c>
-      <c r="G87" s="16" t="inlineStr">
+      <c r="G96" s="27" t="inlineStr">
         <is>
           <t>Naukri</t>
         </is>
       </c>
-      <c r="H87" s="18" t="n">
+      <c r="H96" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="I87" s="19">
-        <f>IF(H87="","",TODAY()-H87)</f>
-        <v/>
-      </c>
-      <c r="J87" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K87" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L87" s="18" t="n"/>
-      <c r="M87" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N87" s="17" t="inlineStr">
+      <c r="I96" s="29">
+        <f>IF(H96="","",TODAY()-H96)</f>
+        <v/>
+      </c>
+      <c r="J96" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K96" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L96" s="28" t="n"/>
+      <c r="M96" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N96" s="17" t="inlineStr">
         <is>
           <t>Auto-added; check company/location</t>
         </is>
       </c>
-      <c r="O87" s="18" t="n">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="16" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="16">
-        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E88)),ISNUMBER(SEARCH("thane",E88)),ISNUMBER(SEARCH("remote",E88))),"1 Mumbai/Remote",IF(OR(E88="",E88="Verify"),"2 Verify location","3 Other city"))</f>
-        <v/>
-      </c>
-      <c r="C88" s="17" t="inlineStr">
+      <c r="O96" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="27" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E97)),ISNUMBER(SEARCH("thane",E97)),ISNUMBER(SEARCH("remote",E97))),"1 Mumbai/Remote",IF(OR(E97="",E97="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C97" s="17" t="inlineStr">
+        <is>
+          <t>Plexohrsolutions</t>
+        </is>
+      </c>
+      <c r="D97" s="17" t="inlineStr">
+        <is>
+          <t>Java Backend Developer</t>
+        </is>
+      </c>
+      <c r="E97" s="17" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="F97" s="27" t="inlineStr">
+        <is>
+          <t>3-5 yrs</t>
+        </is>
+      </c>
+      <c r="G97" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H97" s="28" t="n">
+        <v>46303</v>
+      </c>
+      <c r="I97" s="29">
+        <f>IF(H97="","",TODAY()-H97)</f>
+        <v/>
+      </c>
+      <c r="J97" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K97" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L97" s="28" t="n"/>
+      <c r="M97" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N97" s="17" t="inlineStr">
+        <is>
+          <t>Auto-added; check company/location</t>
+        </is>
+      </c>
+      <c r="O97" s="28" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="27" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="27">
+        <f>IF(OR(ISNUMBER(SEARCH("mumbai",E98)),ISNUMBER(SEARCH("thane",E98)),ISNUMBER(SEARCH("remote",E98))),"1 Mumbai/Remote",IF(OR(E98="",E98="Verify"),"2 Verify location","3 Other city"))</f>
+        <v/>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
         <is>
           <t>Altezzasys</t>
         </is>
       </c>
-      <c r="D88" s="17" t="inlineStr">
+      <c r="D98" s="17" t="inlineStr">
         <is>
           <t>Java Backend Developer</t>
         </is>
       </c>
-      <c r="E88" s="17" t="inlineStr">
+      <c r="E98" s="17" t="inlineStr">
         <is>
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F88" s="16" t="inlineStr">
+      <c r="F98" s="27" t="inlineStr">
         <is>
           <t>4-6 yrs</t>
         </is>
       </c>
-      <c r="G88" s="16" t="inlineStr">
+      <c r="G98" s="27" t="inlineStr">
         <is>
           <t>Naukri</t>
         </is>
       </c>
-      <c r="H88" s="18" t="n">
+      <c r="H98" s="28" t="n">
         <v>46302</v>
       </c>
-      <c r="I88" s="19">
-        <f>IF(H88="","",TODAY()-H88)</f>
-        <v/>
-      </c>
-      <c r="J88" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K88" s="16" t="inlineStr">
-        <is>
-          <t>Not applied</t>
-        </is>
-      </c>
-      <c r="L88" s="18" t="n"/>
-      <c r="M88" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="N88" s="17" t="inlineStr">
+      <c r="I98" s="29">
+        <f>IF(H98="","",TODAY()-H98)</f>
+        <v/>
+      </c>
+      <c r="J98" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K98" s="27" t="inlineStr">
+        <is>
+          <t>Not applied</t>
+        </is>
+      </c>
+      <c r="L98" s="28" t="n"/>
+      <c r="M98" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N98" s="17" t="inlineStr">
         <is>
           <t>At the 7-day edge</t>
         </is>
       </c>
-      <c r="O88" s="18" t="n">
+      <c r="O98" s="28" t="n">
         <v>46309</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O88"/>
+  <autoFilter ref="A1:O98"/>
   <conditionalFormatting sqref="J2:J1000">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="7" text="" percent="0" bottom="0">
       <formula>"High"</formula>
@@ -6452,6 +7114,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId97"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
